--- a/data/output/workbook/2026-07-01.xlsx
+++ b/data/output/workbook/2026-07-01.xlsx
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10353675"/>
+    <ext cx="10125075" cy="10582275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 07:25</t>
+          <t>2026-07-01 10:29</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6675,249 +6675,174 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F68" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G68" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H68" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I68" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J68" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K68" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L68" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M68" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N68" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O68" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P68" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q68" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.718</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>5.967</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>5.276</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>8.778</v>
+        <v>4.718</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.4</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>6.55</v>
       </c>
       <c r="O69" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>5.967</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>5.276</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.956</v>
+        <v>8.778</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.167</v>
+        <v>7.5</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -6970,33 +6895,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O70" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.244</v>
+        <v>0.956</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>7.667</v>
+        <v>1.167</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -7049,320 +6970,324 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>8.208</v>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B73" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C73" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E73" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F73" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G73" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H73" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr">
+      <c r="I73" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J72" s="34" t="inlineStr">
+      <c r="J73" s="34" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K73" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L73" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M73" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N73" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O73" s="32" t="n">
         <v>1.133</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P73" s="32" t="n">
         <v>0.822</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q73" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F76" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G76" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H76" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I76" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J76" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K76" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L76" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M76" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N76" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O76" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P76" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.211</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>4.493</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>7.792</v>
+        <v>4.211</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H77" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>3.5</v>
       </c>
       <c r="O77" s="32" t="n">
-        <v>11.667</v>
+        <v>4.5</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>4.493</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.896</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>1</v>
+        <v>8.6</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -7415,33 +7340,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O78" s="32" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>8.467000000000001</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.021000000000001</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -7494,76 +7415,155 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>7.778</v>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B81" s="32" t="n">
         <v>0.466</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C81" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D81" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H80" s="36" t="inlineStr">
+      <c r="H81" s="36" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr">
+      <c r="I81" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="J81" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K81" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L81" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M81" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N81" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O81" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P81" s="32" t="n">
         <v>0.493</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8584,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Over 167.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6595269230769231</v>
+        <v>0.6154411764705883</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-194</v>
+        <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8836,37 +8836,37 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Atlanta Dream @ Washington Mystics</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5816097560975609</v>
+        <v>0.3552321981424149</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-139</v>
+        <v>182</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 35.5% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3510810810810811</v>
+        <v>0.3901748251748251</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8973,32 +8973,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Atlanta Dream @ Washington Mystics</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Washington Mystics +6.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3996402877697841</v>
+        <v>0.5619058823529411</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>150</v>
+        <v>-128</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>-104</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9039,32 +9039,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5475</v>
+        <v>0.4870403587443947</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-121</v>
+        <v>105</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9105,32 +9105,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics +6.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5551764705882353</v>
+        <v>0.4226953125</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-125</v>
+        <v>137</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-104</v>
+        <v>156</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9171,12 +9171,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9186,17 +9186,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.425234375</v>
+        <v>0.5499254901960784</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>135</v>
+        <v>-122</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>156</v>
+        <v>-104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9237,12 +9237,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Dallas Wings @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +6.5</t>
+          <t>Connecticut Sun +8.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5319607843137254</v>
+        <v>0.5634619047619048</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-114</v>
+        <v>-129</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>-110</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9298,37 +9298,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4877477477477478</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9369,12 +9369,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Seattle Storm</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5554730769230769</v>
+        <v>0.3539666666666667</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-125</v>
+        <v>183</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-108</v>
+        <v>200</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 35.4% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9430,37 +9430,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Connecticut Sun</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun +8.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5581714285714287</v>
+        <v>0.4655506607929515</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-126</v>
+        <v>115</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-110</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9496,37 +9496,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5306</v>
+        <v>0.4736486486486488</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-113</v>
+        <v>111</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9567,12 +9567,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.353</v>
+        <v>0.6614259259259259</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>183</v>
+        <v>-195</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>200</v>
+        <v>-170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 35.3% (fair +183). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9628,17 +9628,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.6604185185185184</v>
+        <v>0.4700900900900902</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-194</v>
+        <v>113</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-170</v>
+        <v>122</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9694,17 +9694,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9714,17 +9714,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4724324324324325</v>
+        <v>0.4596916299559472</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9760,7 +9760,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -9784,13 +9784,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4650222222222222</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9826,37 +9826,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5468047619047619</v>
+        <v>0.4779629629629629</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-121</v>
+        <v>109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-110</v>
+        <v>116</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9897,12 +9897,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9912,17 +9912,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4591189427312775</v>
+        <v>0.4646846846846848</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9963,12 +9963,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9978,17 +9978,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4588105726872247</v>
+        <v>0.5126500000000001</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>118</v>
+        <v>-105</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10021,273 +10021,9 @@
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>San Diego Padres</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>0.4762672811059908</v>
-      </c>
-      <c r="G25" s="14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>117</v>
-      </c>
-      <c r="I25" s="13">
-        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
-        <v/>
-      </c>
-      <c r="J25" s="16">
-        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
-        <v/>
-      </c>
-      <c r="K25" s="17">
-        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L25" s="18">
-        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N25" s="19" t="inlineStr">
-        <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
-        </is>
-      </c>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="16">
-        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>23:40</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Kansas City Royals</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>0.4646846846846848</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>115</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="I26" s="13">
-        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
-        <v/>
-      </c>
-      <c r="J26" s="16">
-        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L26" s="18">
-        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
-        </is>
-      </c>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="16">
-        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>17:10</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Texas Rangers</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>0.51165</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>-105</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I27" s="13">
-        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
-        <v/>
-      </c>
-      <c r="J27" s="16">
-        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
-        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L27" s="18">
-        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M27" s="12">
-        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N27" s="19" t="inlineStr">
-        <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
-        </is>
-      </c>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="16">
-        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>00:05</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Detroit Tigers</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>0.4796713615023475</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="I28" s="13">
-        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
-        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L28" s="18">
-        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
-        </is>
-      </c>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="16">
-        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J28">
+  <conditionalFormatting sqref="J5:J24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10453,10 +10189,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4591189427312775</v>
+        <v>0.4655506607929515</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>127</v>
@@ -10483,7 +10219,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10519,10 +10255,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5408409691629956</v>
+        <v>0.5344629955947137</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-127</v>
@@ -10549,7 +10285,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10585,13 +10321,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4595</v>
+        <v>0.4757</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10615,7 +10351,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10651,13 +10387,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5405</v>
+        <v>0.5243</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-118</v>
+        <v>-110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10681,7 +10417,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10717,10 +10453,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3826</v>
+        <v>0.3639</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>150</v>
@@ -10747,7 +10483,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10783,10 +10519,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6361</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-161</v>
+        <v>-175</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>144</v>
@@ -10813,7 +10549,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10849,7 +10585,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.51165</v>
+        <v>0.5126500000000001</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-105</v>
@@ -10879,7 +10615,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10915,13 +10651,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4883411764705882</v>
+        <v>0.4873472906403941</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10945,7 +10681,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10981,13 +10717,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4976</v>
+        <v>0.4877</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11011,7 +10747,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11047,13 +10783,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5024</v>
+        <v>0.5123</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-101</v>
+        <v>-105</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -11077,7 +10813,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11113,10 +10849,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.326</v>
+        <v>0.3244</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>180</v>
@@ -11143,7 +10879,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 32.6% (fair +207). Your call.</t>
+          <t>Model 32.4% (fair +208). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11179,13 +10915,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6739999999999999</v>
+        <v>0.6756</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-207</v>
+        <v>-208</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -11209,7 +10945,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 67.4% (fair -207). Your call.</t>
+          <t>Model 67.6% (fair -208). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11251,7 +10987,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11383,7 +11119,7 @@
         <v>157</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11449,7 +11185,7 @@
         <v>-157</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11641,13 +11377,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.444625550660793</v>
+        <v>0.4454222222222222</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11707,10 +11443,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5553872246696036</v>
+        <v>0.5545480176211454</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-127</v>
@@ -11737,7 +11473,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.5% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11769,17 +11505,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4525365853658537</v>
+        <v>0.4444</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11803,7 +11539,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11835,17 +11571,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5475</v>
+        <v>0.5556</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-121</v>
+        <v>-125</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11869,7 +11605,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11905,10 +11641,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4153</v>
+        <v>0.411</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>150</v>
@@ -11935,7 +11671,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11971,13 +11707,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5847</v>
+        <v>0.589</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-141</v>
+        <v>-143</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -12001,7 +11737,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12037,13 +11773,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4762672811059908</v>
+        <v>0.4779629629629629</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12067,7 +11803,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12103,10 +11839,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5237185185185185</v>
+        <v>0.5220537037037037</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-116</v>
@@ -12133,7 +11869,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12165,17 +11901,17 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 12</t>
+          <t>Over 12.5</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4184121951219512</v>
+        <v>0.2438</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>139</v>
+        <v>310</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>-105</v>
+        <v>113</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -12199,7 +11935,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 24.4% (fair +310). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12231,14 +11967,14 @@
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 12</t>
+          <t>Under 12.5</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5816097560975609</v>
+        <v>0.7562</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-139</v>
+        <v>-310</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>105</v>
@@ -12265,7 +12001,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 75.6% (fair -310). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12301,13 +12037,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3694</v>
+        <v>0.3672</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12331,7 +12067,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 36.7% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12367,10 +12103,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6306</v>
+        <v>0.6328</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>163</v>
@@ -12397,7 +12133,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12433,13 +12169,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5148173076923077</v>
+        <v>0.5120980392156862</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12463,7 +12199,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12499,10 +12235,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4851960784313725</v>
+        <v>0.4879411764705882</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>104</v>
@@ -12529,7 +12265,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12565,13 +12301,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3967</v>
+        <v>0.4037</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12595,7 +12331,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12631,13 +12367,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-152</v>
+        <v>-148</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12661,7 +12397,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12697,7 +12433,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4588105726872247</v>
+        <v>0.4596916299559472</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>118</v>
@@ -12727,7 +12463,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.0% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12763,13 +12499,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5411766519823789</v>
+        <v>0.5403353711790393</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-118</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-127</v>
+        <v>-129</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12793,7 +12529,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.0% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12825,17 +12561,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5709</v>
+        <v>0.5766</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-133</v>
+        <v>-136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12859,7 +12595,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12891,17 +12627,17 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4291</v>
+        <v>0.4234</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12925,7 +12661,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12961,13 +12697,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3746</v>
+        <v>0.3733</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12991,7 +12727,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13027,13 +12763,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6254</v>
+        <v>0.6267</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-117</v>
+        <v>-116</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13057,7 +12793,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13093,13 +12829,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4650222222222222</v>
+        <v>0.4700900900900902</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13123,7 +12859,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13159,13 +12895,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5349665198237886</v>
+        <v>0.5299306306306306</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-127</v>
+        <v>-122</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13189,7 +12925,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13231,7 +12967,7 @@
         <v>158</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -13297,7 +13033,7 @@
         <v>-158</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13363,7 +13099,7 @@
         <v>179</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13429,7 +13165,7 @@
         <v>-179</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-114</v>
+        <v>-119</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13617,17 +13353,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 11</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3922</v>
+        <v>0.3048</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13651,7 +13387,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 30.5% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13683,17 +13419,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.6952</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-155</v>
+        <v>-228</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13717,7 +13453,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 69.5% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13753,13 +13489,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4877477477477478</v>
+        <v>0.4870403587443947</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13783,7 +13519,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13819,7 +13555,7 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5122351351351352</v>
+        <v>0.5130045045045045</v>
       </c>
       <c r="G56" s="14" t="n">
         <v>-105</v>
@@ -13849,7 +13585,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13881,17 +13617,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5306</v>
+        <v>0.474</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-113</v>
+        <v>111</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13915,7 +13651,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 53.1% (fair -113). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13947,14 +13683,14 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4694146341463415</v>
+        <v>0.526</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>113</v>
+        <v>-111</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>105</v>
@@ -13981,7 +13717,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 46.9% (fair +113). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14023,7 +13759,7 @@
         <v>209</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14089,7 +13825,7 @@
         <v>-209</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-125</v>
+        <v>-123</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14793,10 +14529,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.3395925925925926</v>
+        <v>0.3385555555555556</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>170</v>
@@ -14823,7 +14559,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14859,10 +14595,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.6604185185185184</v>
+        <v>0.6614259259259259</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-194</v>
+        <v>-195</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>-170</v>
@@ -14889,7 +14625,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14925,10 +14661,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.555611013215859</v>
+        <v>0.5542123348017621</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>-127</v>
@@ -14955,7 +14691,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14991,10 +14727,10 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4444052863436123</v>
+        <v>0.4457709251101322</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H74" s="15" t="n">
         <v>127</v>
@@ -15021,7 +14757,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15057,13 +14793,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5554730769230769</v>
+        <v>0.5499254901960784</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15087,7 +14823,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15123,10 +14859,10 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4445098039215686</v>
+        <v>0.4500980392156863</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H76" s="15" t="n">
         <v>104</v>
@@ -15153,7 +14889,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15189,13 +14925,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4901442307692308</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15219,7 +14955,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15255,10 +14991,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5098793427230046</v>
+        <v>0.5136990610328639</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-113</v>
@@ -15285,7 +15021,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15321,10 +15057,10 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5275783410138248</v>
+        <v>0.5263921658986175</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H79" s="15" t="n">
         <v>-117</v>
@@ -15351,7 +15087,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15387,10 +15123,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4724324324324325</v>
+        <v>0.4736486486486488</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>122</v>
@@ -15417,7 +15153,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15453,13 +15189,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4796713615023475</v>
+        <v>0.5036</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>108</v>
+        <v>-101</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15483,7 +15219,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15519,13 +15255,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5202995391705069</v>
+        <v>0.4964</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-108</v>
+        <v>101</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-117</v>
+        <v>-113</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15549,7 +15285,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15585,13 +15321,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.3996402877697841</v>
+        <v>0.3901748251748251</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15615,7 +15351,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15651,13 +15387,13 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.6003518518518518</v>
+        <v>0.6098328671328671</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-170</v>
+        <v>-186</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15681,7 +15417,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15717,10 +15453,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.425234375</v>
+        <v>0.4226953125</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>156</v>
@@ -15747,7 +15483,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15783,10 +15519,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5747625000000001</v>
+        <v>0.5772609375000001</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-135</v>
+        <v>-137</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-156</v>
@@ -15813,7 +15549,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15990,13 +15726,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6489176470588235</v>
+        <v>0.6447732732732733</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-185</v>
+        <v>-182</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-240</v>
+        <v>-233</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16020,7 +15756,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 64.9% (fair -185). Your call.</t>
+          <t>Model 64.5% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16056,13 +15792,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3510810810810811</v>
+        <v>0.3552321981424149</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16086,7 +15822,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 35.5% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16118,17 +15854,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Over 167.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6595269230769231</v>
+        <v>0.6154411764705883</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-194</v>
+        <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16152,7 +15888,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -16184,17 +15920,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 165.5</t>
+          <t>Under 167.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3405</v>
+        <v>0.3846000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-108</v>
+        <v>104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16218,7 +15954,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 34.1% (fair +194). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -16254,10 +15990,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5551764705882353</v>
+        <v>0.5619058823529411</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-104</v>
@@ -16284,7 +16020,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -16320,13 +16056,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4448</v>
+        <v>0.4381042654028435</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -16350,7 +16086,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -16514,17 +16250,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 171.5</t>
+          <t>Over 172.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.442252380952381</v>
+        <v>0.4191079812206573</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -16548,7 +16284,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -16580,17 +16316,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 171.5</t>
+          <t>Under 172.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5578000000000001</v>
+        <v>0.5809</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-126</v>
+        <v>-139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -16614,7 +16350,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16650,10 +16386,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5581714285714287</v>
+        <v>0.5634619047619048</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-126</v>
+        <v>-129</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-110</v>
@@ -16680,7 +16416,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16716,13 +16452,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4418269230769231</v>
+        <v>0.4365437788018434</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16746,7 +16482,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16782,7 +16518,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.353</v>
+        <v>0.3539666666666667</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>183</v>
@@ -16812,7 +16548,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 35.3% (fair +183). Your call.</t>
+          <t>Model 35.4% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16848,13 +16584,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6469829431438127</v>
+        <v>0.6460727891156463</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-183</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-199</v>
+        <v>-194</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16878,7 +16614,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 64.7% (fair -183). Your call.</t>
+          <t>Model 64.6% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16910,17 +16646,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 168.5</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5468047619047619</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-121</v>
+        <v>100</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -16944,7 +16680,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -16976,17 +16712,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 168.5</t>
+          <t>Under 170.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4532</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17010,7 +16746,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17046,13 +16782,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4680509803921569</v>
+        <v>0.4263</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-104</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17076,7 +16812,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -17112,10 +16848,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5319607843137254</v>
+        <v>0.5737</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-114</v>
+        <v>-135</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>104</v>
@@ -17142,7 +16878,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>

--- a/data/output/workbook/2026-07-01.xlsx
+++ b/data/output/workbook/2026-07-01.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10734675"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10696575"/>
+    <ext cx="10125075" cy="10277475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10582275"/>
+    <ext cx="10125075" cy="10182225"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 10:29</t>
+          <t>2026-07-01 13:14</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,891 +2091,891 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Detroit Tigers offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>4.288</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>3.737</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Detroit Tigers offense vs New York Yankees defense</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.288</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.55</v>
+        <v>8.167</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.433</v>
+        <v>8.6</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>3.737</v>
+        <v>8.435</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Detroit Tigers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>3.986</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
-        <v>7.755</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>7.609</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="B76" s="32" t="n">
+        <v>8.109</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>7.592</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="B77" s="32" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>8.435</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Detroit Tigers defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.776</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>8.4</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>3.45</v>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>3.7</v>
+        <v>7.333</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>3.986</v>
+        <v>7.776</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.109</v>
+        <v>0.634</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.433</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>0.25</v>
       </c>
       <c r="O79" s="32" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>7.592</v>
+        <v>0.37</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.634</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H82" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6658,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6675,174 +6675,328 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F66" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H66" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I66" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J66" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K66" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L66" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M66" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N66" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O66" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P66" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q66" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>4.718</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D67" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E67" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F67" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G67" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H67" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>5.967</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>8.778</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.718</v>
+        <v>0.956</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>5.967</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>5.276</v>
+        <v>1.167</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.778</v>
+        <v>7.244</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>7.5</v>
+        <v>7.667</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -6896,398 +7050,398 @@
         </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.603999999999999</v>
+        <v>8.208</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>0.956</v>
+        <v>0.536</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H71" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>0.822</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>7.244</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.208</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B74" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F74" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H74" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J74" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K74" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M74" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N74" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O74" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P74" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>4.211</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
+      <c r="K75" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>4.493</v>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.211</v>
+        <v>0.896</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>1</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>4.493</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.792</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -7341,229 +7495,75 @@
         </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>11.667</v>
+        <v>6.667</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>7.778</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.896</v>
+        <v>0.466</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.8</v>
+      </c>
+      <c r="D79" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E79" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F79" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G79" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J79" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M79" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="N79" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>0.493</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>8.021000000000001</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>7.778</v>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H81" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J81" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7582,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7599,174 +7599,249 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs Houston Astros defense</t>
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.921</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>4.77</v>
+        <v>7.776</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="32" t="n">
-        <v>4.767</v>
+        <v>6.75</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>4.921</v>
+        <v>7.625</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -7819,29 +7894,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>7.625</v>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -7894,328 +7973,324 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O72" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>8.417</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.939</v>
+        <v>0.662</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.767</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="O73" s="32" t="n">
-        <v>9</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P73" s="32" t="n">
-        <v>8.417</v>
+        <v>0.635</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="C77" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="29" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Minnesota Twins defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J77" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O77" s="32" t="n">
+        <v>6.033</v>
+      </c>
+      <c r="P77" s="32" t="n">
+        <v>5.162</v>
+      </c>
+      <c r="Q77" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>4.882</v>
+        <v>8.083</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D78" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E78" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F78" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G78" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L78" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M78" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N78" s="32" t="n">
-        <v>5.9</v>
+        <v>7.25</v>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="32" t="n">
-        <v>6.033</v>
+        <v>10</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>5.162</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -8268,29 +8343,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>8.305999999999999</v>
+      <c r="O79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -8343,151 +8422,72 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O80" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P80" s="32" t="n">
+        <v>8.265000000000001</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="32" t="n">
-        <v>7.729</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="C81" s="32" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.667</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G81" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M81" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N81" s="32" t="n">
+        <v>0.45</v>
       </c>
       <c r="O81" s="32" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="P81" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="Q81" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="C82" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G82" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I82" s="32" t="inlineStr"/>
-      <c r="J82" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M82" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N82" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O82" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P82" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8584,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8728,13 +8728,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6154411764705883</v>
+        <v>0.6154460093896714</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8794,13 +8794,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2868585131894484</v>
+        <v>0.2926</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 28.7% (fair +249). Your call.</t>
+          <t>Model 29.3% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8856,17 +8856,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3552321981424149</v>
+        <v>0.406037037037037</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +182). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8902,17 +8902,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3901748251748251</v>
+        <v>0.4812775330396476</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>156</v>
+        <v>108</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5619058823529411</v>
+        <v>0.5551764705882353</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-128</v>
+        <v>-125</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-104</v>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9034,17 +9034,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4870403587443947</v>
+        <v>0.425234375</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9105,12 +9105,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4226953125</v>
+        <v>0.54355</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>137</v>
+        <v>-119</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9166,17 +9166,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9190,13 +9190,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5499254901960784</v>
+        <v>0.44701244813278</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-122</v>
+        <v>124</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-104</v>
+        <v>141</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9237,32 +9237,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Connecticut Sun</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun +8.5</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5634619047619048</v>
+        <v>0.5</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-129</v>
+        <v>100</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9298,34 +9298,34 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5</v>
+        <v>0.498075117370892</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9364,17 +9364,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3539666666666667</v>
+        <v>0.4650220264317181</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4655506607929515</v>
+        <v>0.4529184549356223</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4736486486486488</v>
+        <v>0.6621814814814815</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>111</v>
+        <v>-196</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9577,22 +9577,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6614259259259259</v>
+        <v>0.5506809523809523</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-195</v>
+        <v>-123</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-170</v>
+        <v>-110</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9633,32 +9633,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4700900900900902</v>
+        <v>0.5170443349753694</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>113</v>
+        <v>-107</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9694,37 +9694,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4596916299559472</v>
+        <v>0.4975238095238095</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9765,32 +9765,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Seattle Storm +5.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4862910798122066</v>
+        <v>0.5213</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>106</v>
+        <v>-109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9831,12 +9831,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9846,17 +9846,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4779629629629629</v>
+        <v>0.4625333333333333</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9892,17 +9892,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9912,17 +9912,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4646846846846848</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9958,17 +9958,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9978,17 +9978,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5126500000000001</v>
+        <v>0.4758064516129032</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10021,9 +10021,273 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Chicago Cubs</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.4823943661971832</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.2% (fair +107). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets @ Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>19:07</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>New York Mets</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.4977669902912621</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.8% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.4803286384976526</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.0% (fair +108). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ New York Yankees</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>New York Yankees</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.5459023255813954</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-120</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 54.6% (fair -120). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J24">
+  <conditionalFormatting sqref="J5:J28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10045,7 +10309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P86"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10189,13 +10453,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4655506607929515</v>
+        <v>0.44701244813278</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -10219,7 +10483,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10255,13 +10519,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5344629955947137</v>
+        <v>0.5529836065573771</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-115</v>
+        <v>-124</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-127</v>
+        <v>-144</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -10285,7 +10549,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10321,13 +10585,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4757</v>
+        <v>0.4684</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10351,7 +10615,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 46.8% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10387,13 +10651,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5243</v>
+        <v>0.5316000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10417,7 +10681,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.2% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10453,13 +10717,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3639</v>
+        <v>0.3671</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10483,7 +10747,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.7% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10519,10 +10783,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6361</v>
+        <v>0.6329</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-175</v>
+        <v>-172</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>144</v>
@@ -10549,7 +10813,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10585,13 +10849,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5126500000000001</v>
+        <v>0.498075117370892</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-105</v>
+        <v>101</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10615,7 +10879,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10651,13 +10915,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4873472906403941</v>
+        <v>0.5019403846153846</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>105</v>
+        <v>-101</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-103</v>
+        <v>-108</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10681,7 +10945,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10713,17 +10977,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4877</v>
+        <v>0.4874</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10747,7 +11011,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10779,17 +11043,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5123</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>-105</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10813,7 +11077,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10849,13 +11113,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3244</v>
+        <v>0.3242</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>208</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -10915,13 +11179,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6756</v>
+        <v>0.6758</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-208</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10981,13 +11245,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4999</v>
+        <v>0.4646</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -11011,7 +11275,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11047,13 +11311,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5001</v>
+        <v>0.5354</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-100</v>
+        <v>-115</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -11077,7 +11341,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11113,13 +11377,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3889</v>
+        <v>0.4193</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11143,7 +11407,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 41.9% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11179,13 +11443,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.6111</v>
+        <v>0.5807</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-157</v>
+        <v>-138</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11209,7 +11473,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11245,10 +11509,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.369</v>
+        <v>0.4063</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -11275,7 +11539,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11311,13 +11575,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.631</v>
+        <v>0.5937</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-171</v>
+        <v>-146</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-111</v>
+        <v>-105</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11341,7 +11605,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11377,13 +11641,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4454222222222222</v>
+        <v>0.4540807174887892</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11407,7 +11671,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11443,13 +11707,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5545480176211454</v>
+        <v>0.5459023255813954</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-124</v>
+        <v>-120</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-127</v>
+        <v>-115</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11473,7 +11737,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -124). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11509,10 +11773,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4444</v>
+        <v>0.48295</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>100</v>
@@ -11539,7 +11803,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11575,13 +11839,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5556</v>
+        <v>0.5170443349753694</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-125</v>
+        <v>-107</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11605,7 +11869,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11647,7 +11911,7 @@
         <v>143</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11713,7 +11977,7 @@
         <v>-143</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-113</v>
+        <v>-127</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11773,13 +12037,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4779629629629629</v>
+        <v>0.4823943661971832</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11803,7 +12067,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11839,13 +12103,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5220537037037037</v>
+        <v>0.5175718309859155</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11869,7 +12133,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11905,10 +12169,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.2438</v>
+        <v>0.2359</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -11935,7 +12199,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 24.4% (fair +310). Your call.</t>
+          <t>Model 23.6% (fair +324). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11971,13 +12235,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.7562</v>
+        <v>0.7641</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-310</v>
+        <v>-324</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12001,7 +12265,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 75.6% (fair -310). Your call.</t>
+          <t>Model 76.4% (fair -324). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12037,13 +12301,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3672</v>
+        <v>0.3662</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -12067,7 +12331,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +172). Your call.</t>
+          <t>Model 36.6% (fair +173). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12103,10 +12367,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6328</v>
+        <v>0.6337999999999999</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-172</v>
+        <v>-173</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>163</v>
@@ -12133,7 +12397,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 63.4% (fair -173). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12169,13 +12433,13 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5120980392156862</v>
+        <v>0.4977669902912621</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-105</v>
+        <v>101</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-104</v>
+        <v>106</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -12199,7 +12463,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12235,13 +12499,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4879411764705882</v>
+        <v>0.5022588235294118</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>105</v>
+        <v>-101</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12265,7 +12529,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12307,7 +12571,7 @@
         <v>148</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12373,7 +12637,7 @@
         <v>-148</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12433,13 +12697,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4596916299559472</v>
+        <v>0.4529184549356223</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12463,7 +12727,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +118). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12499,13 +12763,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5403353711790393</v>
+        <v>0.5471094017094017</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-129</v>
+        <v>-134</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12529,7 +12793,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -118). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12561,7 +12825,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
@@ -12571,7 +12835,7 @@
         <v>-136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12627,7 +12891,7 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
@@ -12637,7 +12901,7 @@
         <v>136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12703,7 +12967,7 @@
         <v>168</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12769,7 +13033,7 @@
         <v>-168</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-116</v>
+        <v>-112</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12829,13 +13093,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4700900900900902</v>
+        <v>0.4650220264317181</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12859,7 +13123,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12895,13 +13159,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5299306306306306</v>
+        <v>0.5349714285714287</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-113</v>
+        <v>-115</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12925,7 +13189,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12961,13 +13225,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.3875</v>
+        <v>0.4487</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12991,7 +13255,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13027,10 +13291,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.6125</v>
+        <v>0.5513</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-158</v>
+        <v>-123</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>105</v>
@@ -13057,7 +13321,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13093,13 +13357,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3579</v>
+        <v>0.3656</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13123,7 +13387,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 36.6% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13159,13 +13423,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6421</v>
+        <v>0.6344000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-179</v>
+        <v>-174</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13189,7 +13453,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 63.4% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13225,10 +13489,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5353162162162162</v>
+        <v>0.5374594594594594</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>-122</v>
@@ -13255,7 +13519,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13291,13 +13555,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4646846846846848</v>
+        <v>0.4625333333333333</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13321,7 +13585,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13489,13 +13753,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4870403587443947</v>
+        <v>0.4812775330396476</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13519,7 +13783,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13555,13 +13819,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5130045045045045</v>
+        <v>0.5186859030837004</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-105</v>
+        <v>-108</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13585,7 +13849,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13617,17 +13881,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.474</v>
+        <v>0.5759</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>111</v>
+        <v>-136</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13651,7 +13915,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13683,17 +13947,17 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.526</v>
+        <v>0.4241</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-111</v>
+        <v>136</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13717,7 +13981,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14269,7 +14533,7 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5867</v>
+        <v>0.5875</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>-142</v>
@@ -14297,7 +14561,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 58.7% (fair -142). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14333,7 +14597,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4133</v>
+        <v>0.4125</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>142</v>
@@ -14361,7 +14625,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 41.3% (fair +142). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14397,13 +14661,13 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4534562211981567</v>
+        <v>0.4498198198198199</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -14427,7 +14691,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14463,10 +14727,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.546527027027027</v>
+        <v>0.550209009009009</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-122</v>
@@ -14493,7 +14757,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14510,32 +14774,32 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.3385555555555556</v>
+        <v>0.5018365384615384</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>195</v>
+        <v>-101</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>170</v>
+        <v>-108</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14559,7 +14823,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 33.9% (fair +195). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14576,32 +14840,32 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.6614259259259259</v>
+        <v>0.4981952380952381</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-195</v>
+        <v>101</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-170</v>
+        <v>-110</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14625,7 +14889,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14642,32 +14906,32 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5542123348017621</v>
+        <v>0.4216521739130435</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-124</v>
+        <v>137</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>-127</v>
+        <v>130</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14691,7 +14955,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 55.4% (fair -124). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14708,32 +14972,32 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4457709251101322</v>
+        <v>0.5783627450980393</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>124</v>
+        <v>-137</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>127</v>
+        <v>-155</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -14757,7 +15021,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 44.6% (fair +124). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14774,12 +15038,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -14789,17 +15053,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.5499254901960784</v>
+        <v>0.3377777777777778</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-122</v>
+        <v>196</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14823,7 +15087,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14840,12 +15104,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -14855,17 +15119,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.4500980392156863</v>
+        <v>0.6621814814814815</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>122</v>
+        <v>-196</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>104</v>
+        <v>-170</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14889,7 +15153,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14906,32 +15170,32 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 6.5</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4862910798122066</v>
+        <v>0.5506809523809523</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>106</v>
+        <v>-123</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>113</v>
+        <v>-110</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14955,7 +15219,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14972,32 +15236,32 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 6.5</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5136990610328639</v>
+        <v>0.4493238095238095</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-106</v>
+        <v>123</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15021,7 +15285,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15038,32 +15302,32 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5263921658986175</v>
+        <v>0.4975238095238095</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-111</v>
+        <v>101</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-117</v>
+        <v>110</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15087,7 +15351,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15104,32 +15368,32 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4736486486486488</v>
+        <v>0.5024782608695653</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>111</v>
+        <v>-101</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>122</v>
+        <v>-130</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15153,7 +15417,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15170,12 +15434,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -15185,17 +15449,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5036</v>
+        <v>0.5527369369369369</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-101</v>
+        <v>-124</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15219,7 +15483,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 55.3% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15236,12 +15500,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -15251,17 +15515,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4964</v>
+        <v>0.4472687224669604</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-113</v>
+        <v>127</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15285,7 +15549,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 44.7% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15302,12 +15566,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15317,17 +15581,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.3901748251748251</v>
+        <v>0.54355</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>156</v>
+        <v>-119</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15351,7 +15615,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15368,12 +15632,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15383,17 +15647,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.6098328671328671</v>
+        <v>0.45645</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-156</v>
+        <v>119</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-186</v>
+        <v>100</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15417,7 +15681,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15434,12 +15698,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -15449,17 +15713,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4226953125</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15483,7 +15747,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15500,12 +15764,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -15515,17 +15779,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5772609375000001</v>
+        <v>0.5136990610328639</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-137</v>
+        <v>-106</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-156</v>
+        <v>-113</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15549,7 +15813,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15558,9 +15822,537 @@
         <v/>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="n">
+        <v>0.5197064516129032</v>
+      </c>
+      <c r="G87" s="14" t="n">
+        <v>-108</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I87" s="13">
+        <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
+        <v/>
+      </c>
+      <c r="J87" s="16">
+        <f>IF($H$87="","",$F$87*IF($H$87&lt;0,-100/$H$87,$H$87/100)-(1-$F$87))</f>
+        <v/>
+      </c>
+      <c r="K87" s="17">
+        <f>IF($H$87="","",MAX(0,($F$87*IF($H$87&lt;0,-100/$H$87,$H$87/100)-(1-$F$87))/IF($H$87&lt;0,-100/$H$87,$H$87/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L87" s="18">
+        <f>IF($H$87="","",ROUND(MIN($K$87,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M87" s="12">
+        <f>IF($J$87="","",IF($J$87&lt;0,"Pass",IF($J$87&lt;'Settings'!$B$4,"Thin",IF($J$87&lt;0.06,"✅ Sharp band",IF($J$87&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N87" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.0% (fair -108). Your call.</t>
+        </is>
+      </c>
+      <c r="O87" s="15" t="n"/>
+      <c r="P87" s="16">
+        <f>IF(OR($H$87="",$O$87=""),"",(1+IF($H$87&lt;0,-100/$H$87,$H$87/100))/(1+IF($O$87&lt;0,-100/$O$87,$O$87/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>Kansas City Royals</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>0.4803286384976526</v>
+      </c>
+      <c r="G88" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="I88" s="13">
+        <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
+        <v/>
+      </c>
+      <c r="J88" s="16">
+        <f>IF($H$88="","",$F$88*IF($H$88&lt;0,-100/$H$88,$H$88/100)-(1-$F$88))</f>
+        <v/>
+      </c>
+      <c r="K88" s="17">
+        <f>IF($H$88="","",MAX(0,($F$88*IF($H$88&lt;0,-100/$H$88,$H$88/100)-(1-$F$88))/IF($H$88&lt;0,-100/$H$88,$H$88/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L88" s="18">
+        <f>IF($H$88="","",ROUND(MIN($K$88,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M88" s="12">
+        <f>IF($J$88="","",IF($J$88&lt;0,"Pass",IF($J$88&lt;'Settings'!$B$4,"Thin",IF($J$88&lt;0.06,"✅ Sharp band",IF($J$88&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N88" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.0% (fair +108). Your call.</t>
+        </is>
+      </c>
+      <c r="O88" s="15" t="n"/>
+      <c r="P88" s="16">
+        <f>IF(OR($H$88="",$O$88=""),"",(1+IF($H$88&lt;0,-100/$H$88,$H$88/100))/(1+IF($O$88&lt;0,-100/$O$88,$O$88/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0.4758064516129032</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="I89" s="13">
+        <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
+        <v/>
+      </c>
+      <c r="J89" s="16">
+        <f>IF($H$89="","",$F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))</f>
+        <v/>
+      </c>
+      <c r="K89" s="17">
+        <f>IF($H$89="","",MAX(0,($F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))/IF($H$89&lt;0,-100/$H$89,$H$89/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L89" s="18">
+        <f>IF($H$89="","",ROUND(MIN($K$89,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M89" s="12">
+        <f>IF($J$89="","",IF($J$89&lt;0,"Pass",IF($J$89&lt;'Settings'!$B$4,"Thin",IF($J$89&lt;0.06,"✅ Sharp band",IF($J$89&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N89" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.6% (fair +110). Your call.</t>
+        </is>
+      </c>
+      <c r="O89" s="15" t="n"/>
+      <c r="P89" s="16">
+        <f>IF(OR($H$89="",$O$89=""),"",(1+IF($H$89&lt;0,-100/$H$89,$H$89/100))/(1+IF($O$89&lt;0,-100/$O$89,$O$89/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>0.5241815668202765</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I90" s="13">
+        <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
+        <v/>
+      </c>
+      <c r="J90" s="16">
+        <f>IF($H$90="","",$F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))</f>
+        <v/>
+      </c>
+      <c r="K90" s="17">
+        <f>IF($H$90="","",MAX(0,($F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))/IF($H$90&lt;0,-100/$H$90,$H$90/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L90" s="18">
+        <f>IF($H$90="","",ROUND(MIN($K$90,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M90" s="12">
+        <f>IF($J$90="","",IF($J$90&lt;0,"Pass",IF($J$90&lt;'Settings'!$B$4,"Thin",IF($J$90&lt;0.06,"✅ Sharp band",IF($J$90&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N90" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.4% (fair -110). Your call.</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="16">
+        <f>IF(OR($H$90="",$O$90=""),"",(1+IF($H$90&lt;0,-100/$H$90,$H$90/100))/(1+IF($O$90&lt;0,-100/$O$90,$O$90/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>0.406037037037037</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="I91" s="13">
+        <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
+        <v/>
+      </c>
+      <c r="J91" s="16">
+        <f>IF($H$91="","",$F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))</f>
+        <v/>
+      </c>
+      <c r="K91" s="17">
+        <f>IF($H$91="","",MAX(0,($F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))/IF($H$91&lt;0,-100/$H$91,$H$91/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L91" s="18">
+        <f>IF($H$91="","",ROUND(MIN($K$91,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M91" s="12">
+        <f>IF($J$91="","",IF($J$91&lt;0,"Pass",IF($J$91&lt;'Settings'!$B$4,"Thin",IF($J$91&lt;0.06,"✅ Sharp band",IF($J$91&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N91" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.6% (fair +146). Your call.</t>
+        </is>
+      </c>
+      <c r="O91" s="15" t="n"/>
+      <c r="P91" s="16">
+        <f>IF(OR($H$91="",$O$91=""),"",(1+IF($H$91&lt;0,-100/$H$91,$H$91/100))/(1+IF($O$91&lt;0,-100/$O$91,$O$91/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>0.5939893536121673</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>-146</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>-163</v>
+      </c>
+      <c r="I92" s="13">
+        <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
+        <v/>
+      </c>
+      <c r="J92" s="16">
+        <f>IF($H$92="","",$F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF($H$92="","",MAX(0,($F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))/IF($H$92&lt;0,-100/$H$92,$H$92/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L92" s="18">
+        <f>IF($H$92="","",ROUND(MIN($K$92,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M92" s="12">
+        <f>IF($J$92="","",IF($J$92&lt;0,"Pass",IF($J$92&lt;'Settings'!$B$4,"Thin",IF($J$92&lt;0.06,"✅ Sharp band",IF($J$92&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N92" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.4% (fair -146). Your call.</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="n"/>
+      <c r="P92" s="16">
+        <f>IF(OR($H$92="",$O$92=""),"",(1+IF($H$92&lt;0,-100/$H$92,$H$92/100))/(1+IF($O$92&lt;0,-100/$O$92,$O$92/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>0.425234375</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>156</v>
+      </c>
+      <c r="I93" s="13">
+        <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
+        <v/>
+      </c>
+      <c r="J93" s="16">
+        <f>IF($H$93="","",$F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>IF($H$93="","",MAX(0,($F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))/IF($H$93&lt;0,-100/$H$93,$H$93/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>IF($H$93="","",ROUND(MIN($K$93,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M93" s="12">
+        <f>IF($J$93="","",IF($J$93&lt;0,"Pass",IF($J$93&lt;'Settings'!$B$4,"Thin",IF($J$93&lt;0.06,"✅ Sharp band",IF($J$93&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N93" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.5% (fair +135). Your call.</t>
+        </is>
+      </c>
+      <c r="O93" s="15" t="n"/>
+      <c r="P93" s="16">
+        <f>IF(OR($H$93="",$O$93=""),"",(1+IF($H$93&lt;0,-100/$H$93,$H$93/100))/(1+IF($O$93&lt;0,-100/$O$93,$O$93/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>0.5747625000000001</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>-135</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-156</v>
+      </c>
+      <c r="I94" s="13">
+        <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
+        <v/>
+      </c>
+      <c r="J94" s="16">
+        <f>IF($H$94="","",$F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))</f>
+        <v/>
+      </c>
+      <c r="K94" s="17">
+        <f>IF($H$94="","",MAX(0,($F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))/IF($H$94&lt;0,-100/$H$94,$H$94/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L94" s="18">
+        <f>IF($H$94="","",ROUND(MIN($K$94,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M94" s="12">
+        <f>IF($J$94="","",IF($J$94&lt;0,"Pass",IF($J$94&lt;'Settings'!$B$4,"Thin",IF($J$94&lt;0.06,"✅ Sharp band",IF($J$94&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N94" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.5% (fair -135). Your call.</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="16">
+        <f>IF(OR($H$94="",$O$94=""),"",(1+IF($H$94&lt;0,-100/$H$94,$H$94/100))/(1+IF($O$94&lt;0,-100/$O$94,$O$94/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J86">
+  <conditionalFormatting sqref="J5:J94">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -15726,13 +16518,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6447732732732733</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-182</v>
+        <v>-148</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-233</v>
+        <v>-203</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -15756,7 +16548,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -182). Your call.</t>
+          <t>Model 59.6% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -15792,13 +16584,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3552321981424149</v>
+        <v>0.4037</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -15822,7 +16614,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +182). Your call.</t>
+          <t>Model 40.4% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -15858,13 +16650,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6154411764705883</v>
+        <v>0.6154460093896714</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -15930,7 +16722,7 @@
         <v>160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -15990,10 +16782,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5619058823529411</v>
+        <v>0.5551764705882353</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-128</v>
+        <v>-125</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-104</v>
@@ -16020,7 +16812,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -16056,13 +16848,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4381042654028435</v>
+        <v>0.4448</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -16086,7 +16878,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -16122,13 +16914,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7131359712230216</v>
+        <v>0.7074295918367347</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-249</v>
+        <v>-242</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-317</v>
+        <v>-292</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16152,7 +16944,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 71.3% (fair -249). Your call.</t>
+          <t>Model 70.7% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16188,13 +16980,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2868585131894484</v>
+        <v>0.2926</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -16218,7 +17010,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 28.7% (fair +249). Your call.</t>
+          <t>Model 29.3% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16386,10 +17178,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5634619047619048</v>
+        <v>0.5949</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-129</v>
+        <v>-147</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>-110</v>
@@ -16416,7 +17208,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16452,13 +17244,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4365437788018434</v>
+        <v>0.4051</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16482,7 +17274,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16518,13 +17310,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3539666666666667</v>
+        <v>0.3692</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16548,7 +17340,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16584,13 +17376,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6460727891156463</v>
+        <v>0.6308259259259259</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-183</v>
+        <v>-171</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-194</v>
+        <v>-170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16614,7 +17406,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -16778,17 +17570,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury -6.5</t>
+          <t>Phoenix Mercury -5.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4263</v>
+        <v>0.4787</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -16812,7 +17604,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 42.6% (fair +135). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -16844,17 +17636,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +6.5</t>
+          <t>Seattle Storm +5.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5737</v>
+        <v>0.5213</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-135</v>
+        <v>-109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -16878,7 +17670,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 57.4% (fair -135). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>

--- a/data/output/workbook/2026-07-01.xlsx
+++ b/data/output/workbook/2026-07-01.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10315575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10277475"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -611,7 +611,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10182225"/>
+    <ext cx="10125075" cy="10734675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 13:14</t>
+          <t>2026-07-01 15:51</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,891 +2091,891 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs New York Yankees defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>4.288</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>7.755</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>7.609</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>4.288</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.767</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.55</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>8.6</v>
+        <v>4.433</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.435</v>
+        <v>3.737</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.435</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.55</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J71" s="34" t="inlineStr">
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.479</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>New York Yankees offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>4.776</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>3.986</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.109</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.592</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>9.130000000000001</v>
+        <v>4.776</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4.733</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.45</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>7.333</v>
+        <v>3.7</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.776</v>
+        <v>3.986</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.109</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.592</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.634</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="36" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6658,7 +6658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6675,895 +6675,895 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Tampa Bay Rays offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D66" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E66" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F66" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G66" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H66" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I66" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J66" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K66" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L66" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M66" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N66" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O66" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P66" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q66" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>4.718</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J67" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>5.967</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>5.276</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.603999999999999</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>1.167</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.244</v>
+        <v>4.718</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.4</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>6.55</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>9.6</v>
+        <v>5.967</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>8.208</v>
+        <v>5.276</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>8.778</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>8.603999999999999</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>7.244</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.208</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B71" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.536</v>
       </c>
-      <c r="C71" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.633</v>
       </c>
-      <c r="D71" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="E71" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.733</v>
       </c>
-      <c r="F71" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G71" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>1.4</v>
       </c>
-      <c r="H71" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="I71" s="32" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J71" s="34" t="inlineStr">
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>24th</t>
         </is>
       </c>
-      <c r="K71" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="L71" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>1.1</v>
       </c>
-      <c r="M71" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.867</v>
       </c>
-      <c r="N71" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>1.15</v>
       </c>
-      <c r="O71" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>1.133</v>
       </c>
-      <c r="P71" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.822</v>
       </c>
-      <c r="Q71" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Tampa Bay Rays defense</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E74" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F74" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G74" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H74" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I74" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J74" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K74" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L74" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M74" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N74" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O74" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P74" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q74" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>4.211</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>4.493</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>7.792</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>11.667</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>8.467000000000001</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.896</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.021000000000001</v>
+        <v>4.211</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.5</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>6.667</v>
+        <v>4.5</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>7.778</v>
+        <v>4.493</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>7.792</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>11.667</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8.021000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B79" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.466</v>
       </c>
-      <c r="C79" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="D79" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E79" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="F79" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="G79" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="H79" s="36" t="inlineStr">
+      <c r="H82" s="36" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="J79" s="36" t="inlineStr">
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K79" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L79" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="M79" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="N79" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O79" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P79" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.493</v>
       </c>
-      <c r="Q79" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7582,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7599,174 +7599,249 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs Houston Astros defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs Houston Astros defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J68" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.921</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.77</v>
+        <v>7.776</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>4.767</v>
+        <v>6.75</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.921</v>
+        <v>7.625</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.776</v>
+        <v>1.061</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -7819,29 +7894,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O70" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.625</v>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.061</v>
+        <v>8.939</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -7894,328 +7973,324 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O71" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>8.417</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.939</v>
+        <v>0.662</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.767</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.75</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>9</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.417</v>
+        <v>0.635</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Houston Astros offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>4.882</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H76" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Houston Astros offense vs Minnesota Twins defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="J76" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>6.033</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>5.162</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>4.882</v>
+        <v>8.083</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.9</v>
+        <v>7.25</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr"/>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>6.033</v>
+        <v>10</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>5.162</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.083</v>
+        <v>1.417</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>7.25</v>
+        <v>1</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -8268,29 +8343,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O78" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>8.305999999999999</v>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.417</v>
+        <v>7.729</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>1</v>
+        <v>9.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -8343,151 +8422,72 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O79" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.265000000000001</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.729</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.667</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.45</v>
       </c>
       <c r="O80" s="32" t="n">
-        <v>10.4</v>
+        <v>0.7</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8584,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8728,13 +8728,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6154460093896714</v>
+        <v>0.6154411764705883</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Atlanta Dream @ Washington Mystics</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8856,17 +8856,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.406037037037037</v>
+        <v>0.356656346749226</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>223</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 35.7% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4812775330396476</v>
+        <v>0.4771244635193133</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8973,12 +8973,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8988,17 +8988,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics +6.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5551764705882353</v>
+        <v>0.4812608695652174</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-125</v>
+        <v>108</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-104</v>
+        <v>130</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.425234375</v>
+        <v>0.3977898550724638</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9105,32 +9105,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Atlanta Dream @ Washington Mystics</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Washington Mystics +6.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.54355</v>
+        <v>0.5551764705882353</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-119</v>
+        <v>-125</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9166,17 +9166,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9186,17 +9186,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.44701244813278</v>
+        <v>0.4226953125</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9232,17 +9232,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5369154228855721</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>100</v>
+        <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9298,17 +9298,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.498075117370892</v>
+        <v>0.5445725490196078</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>101</v>
+        <v>-120</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9364,37 +9364,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4650220264317181</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4529184549356223</v>
+        <v>0.4411203319502074</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9496,37 +9496,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.6621814814814815</v>
+        <v>0.5209803921568628</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-196</v>
+        <v>-109</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-170</v>
+        <v>104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9562,37 +9562,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Over 6.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5506809523809523</v>
+        <v>0.4986854460093897</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-123</v>
+        <v>101</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-110</v>
+        <v>113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9633,32 +9633,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5170443349753694</v>
+        <v>0.4533905579399142</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-107</v>
+        <v>121</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9694,37 +9694,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4975238095238095</v>
+        <v>0.5160784313725489</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>-107</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9765,32 +9765,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +5.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.6614259259259259</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-109</v>
+        <v>-195</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>-170</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9826,17 +9826,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9846,17 +9846,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4625333333333333</v>
+        <v>0.4721171171171172</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9897,32 +9897,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Seattle Storm +5.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4862910798122066</v>
+        <v>0.5213</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>106</v>
+        <v>-109</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9958,17 +9958,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9978,17 +9978,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4758064516129032</v>
+        <v>0.4582378854625551</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4823943661971832</v>
+        <v>0.4684684684684685</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 46.8% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10095,32 +10095,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4977669902912621</v>
+        <v>0.5712567567567568</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>101</v>
+        <v>-133</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>106</v>
+        <v>-122</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10161,32 +10161,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4803286384976526</v>
+        <v>0.4237551020408163</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10222,17 +10222,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -10242,17 +10242,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5459023255813954</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-120</v>
+        <v>106</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-115</v>
+        <v>113</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -10285,9 +10285,75 @@
         <v/>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.5258195121951219</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.6% (fair -111). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J28">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10309,7 +10375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P94"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10453,10 +10519,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.44701244813278</v>
+        <v>0.4411203319502074</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>141</v>
@@ -10483,7 +10549,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10519,10 +10585,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5529836065573771</v>
+        <v>0.5588852459016393</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-144</v>
@@ -10549,7 +10615,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10581,17 +10647,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4684</v>
+        <v>0.4575</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10615,7 +10681,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +113). Your call.</t>
+          <t>Model 45.8% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10647,17 +10713,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5316000000000001</v>
+        <v>0.5425</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-113</v>
+        <v>-119</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10681,7 +10747,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -113). Your call.</t>
+          <t>Model 54.2% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10717,10 +10783,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3671</v>
+        <v>0.3816</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>144</v>
@@ -10747,7 +10813,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 36.7% (fair +172). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10783,10 +10849,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6329</v>
+        <v>0.6184000000000001</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-172</v>
+        <v>-162</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>144</v>
@@ -10813,7 +10879,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10849,7 +10915,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.498075117370892</v>
+        <v>0.4986854460093897</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>101</v>
@@ -10879,7 +10945,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10915,7 +10981,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5019403846153846</v>
+        <v>0.5013173076923076</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-101</v>
@@ -10945,7 +11011,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10977,17 +11043,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4874</v>
+        <v>0.5209803921568628</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>105</v>
+        <v>-109</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -11011,7 +11077,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11043,14 +11109,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.479</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-105</v>
+        <v>109</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -11077,7 +11143,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11113,7 +11179,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3242</v>
+        <v>0.3244</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>208</v>
@@ -11179,7 +11245,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6758</v>
+        <v>0.6756</v>
       </c>
       <c r="G16" s="14" t="n">
         <v>-208</v>
@@ -11245,10 +11311,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4646</v>
+        <v>0.4636</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>138</v>
@@ -11275,7 +11341,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.4% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11311,10 +11377,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5354</v>
+        <v>0.5364</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>141</v>
@@ -11341,7 +11407,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.6% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11373,17 +11439,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4193</v>
+        <v>0.4103</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -11407,7 +11473,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +138). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11439,17 +11505,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5807</v>
+        <v>0.5897</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -11473,7 +11539,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -138). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11509,10 +11575,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4063</v>
+        <v>0.41</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -11539,7 +11605,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11575,13 +11641,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5937</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11605,7 +11671,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11641,13 +11707,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4540807174887892</v>
+        <v>0.4579723502304148</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11671,7 +11737,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11707,13 +11773,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5459023255813954</v>
+        <v>0.5420281105990784</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11737,7 +11803,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11773,13 +11839,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.48295</v>
+        <v>0.4838940594059406</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>107</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -11803,7 +11869,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11839,13 +11905,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5170443349753694</v>
+        <v>0.5160784313725489</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>-107</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11869,7 +11935,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11905,13 +11971,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.411</v>
+        <v>0.4117</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>143</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11935,7 +12001,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11971,7 +12037,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.589</v>
+        <v>0.5883</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>-143</v>
@@ -12001,7 +12067,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12037,13 +12103,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4823943661971832</v>
+        <v>0.4851184834123222</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -12067,7 +12133,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12103,13 +12169,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5175718309859155</v>
+        <v>0.5148611374407582</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-113</v>
+        <v>-111</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -12133,7 +12199,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12169,10 +12235,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.2359</v>
+        <v>0.2371</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -12199,7 +12265,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 23.6% (fair +324). Your call.</t>
+          <t>Model 23.7% (fair +322). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12235,13 +12301,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.7641</v>
+        <v>0.7629</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-324</v>
+        <v>-322</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -12265,7 +12331,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 76.4% (fair -324). Your call.</t>
+          <t>Model 76.3% (fair -322). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12301,10 +12367,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3662</v>
+        <v>0.3641</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>163</v>
@@ -12331,7 +12397,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +173). Your call.</t>
+          <t>Model 36.4% (fair +175). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12367,10 +12433,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6337999999999999</v>
+        <v>0.6359</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-173</v>
+        <v>-175</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>163</v>
@@ -12397,7 +12463,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -173). Your call.</t>
+          <t>Model 63.6% (fair -175). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12433,10 +12499,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4977669902912621</v>
+        <v>0.4943203883495145</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>106</v>
@@ -12463,7 +12529,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12499,13 +12565,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5022588235294118</v>
+        <v>0.5056788461538461</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -12529,7 +12595,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12565,13 +12631,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4037</v>
+        <v>0.3994</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -12595,7 +12661,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12631,13 +12697,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6006</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-148</v>
+        <v>-150</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -12661,7 +12727,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12697,7 +12763,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4529184549356223</v>
+        <v>0.4533905579399142</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>121</v>
@@ -12763,13 +12829,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5471094017094017</v>
+        <v>0.5466128755364807</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12835,7 +12901,7 @@
         <v>-136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12967,7 +13033,7 @@
         <v>168</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -13093,13 +13159,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4650220264317181</v>
+        <v>0.4684684684684685</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13123,7 +13189,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 46.8% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13159,13 +13225,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5349714285714287</v>
+        <v>0.5315243243243243</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-115</v>
+        <v>-113</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13189,7 +13255,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 53.2% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13225,10 +13291,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4487</v>
+        <v>0.444</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>117</v>
@@ -13255,7 +13321,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.4% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13291,10 +13357,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5513</v>
+        <v>0.556</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-123</v>
+        <v>-125</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>105</v>
@@ -13321,7 +13387,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.6% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13357,10 +13423,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3656</v>
+        <v>0.3675</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>160</v>
@@ -13387,7 +13453,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 36.6% (fair +174). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13423,13 +13489,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6344000000000001</v>
+        <v>0.6325000000000001</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-174</v>
+        <v>-172</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-121</v>
+        <v>-119</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13453,7 +13519,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 63.4% (fair -174). Your call.</t>
+          <t>Model 63.3% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13489,13 +13555,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5374594594594594</v>
+        <v>0.5417920704845816</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-122</v>
+        <v>-127</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13519,7 +13585,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13555,13 +13621,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4625333333333333</v>
+        <v>0.4582378854625551</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13585,7 +13651,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13617,17 +13683,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 11</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.3048</v>
+        <v>0.4631</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13651,7 +13717,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 30.5% (fair +228). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13683,17 +13749,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 11</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.6952</v>
+        <v>0.5369154228855721</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-228</v>
+        <v>-116</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13717,7 +13783,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -228). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13734,32 +13800,32 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4812775330396476</v>
+        <v>0.5712567567567568</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13783,7 +13849,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13800,32 +13866,32 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Tampa Bay Rays -1.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5186859030837004</v>
+        <v>0.4287557603686636</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-108</v>
+        <v>133</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-127</v>
+        <v>117</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13849,7 +13915,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13876,22 +13942,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5759</v>
+        <v>0.4771244635193133</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-136</v>
+        <v>110</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13915,7 +13981,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13942,22 +14008,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4241</v>
+        <v>0.5228819383259912</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>136</v>
+        <v>-110</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>112</v>
+        <v>-127</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13981,7 +14047,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14008,22 +14074,22 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.3237</v>
+        <v>0.5759</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>209</v>
+        <v>-136</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14047,7 +14113,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 32.4% (fair +209). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14074,22 +14140,22 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.6763</v>
+        <v>0.4241</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-209</v>
+        <v>136</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-123</v>
+        <v>111</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14113,7 +14179,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 67.6% (fair -209). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14130,7 +14196,7 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
@@ -14140,21 +14206,23 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.3178</v>
+        <v>0.3237</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>215</v>
-      </c>
-      <c r="H61" s="15" t="n"/>
+        <v>209</v>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>163</v>
+      </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -14177,7 +14245,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 31.8% (fair +215). Your call.</t>
+          <t>Model 32.4% (fair +209). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -14194,7 +14262,7 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
@@ -14204,21 +14272,23 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Minnesota Twins +1.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.6822</v>
+        <v>0.6763</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-215</v>
-      </c>
-      <c r="H62" s="15" t="n"/>
+        <v>-209</v>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-117</v>
+      </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -14241,7 +14311,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 68.2% (fair -215). Your call.</t>
+          <t>Model 67.6% (fair -209). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -14258,12 +14328,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -14273,14 +14343,14 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.6078</v>
+        <v>0.3178</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-155</v>
+        <v>215</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -14305,7 +14375,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 31.8% (fair +215). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -14322,12 +14392,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -14337,14 +14407,14 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.3922</v>
+        <v>0.6822</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>155</v>
+        <v>-215</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -14369,7 +14439,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 68.2% (fair -215). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -14386,12 +14456,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -14401,14 +14471,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.5264</v>
+        <v>0.6171</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-111</v>
+        <v>-161</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14433,7 +14503,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 61.7% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14450,12 +14520,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -14465,14 +14535,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.4736</v>
+        <v>0.3829</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14497,7 +14567,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 38.3% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14514,7 +14584,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -14529,14 +14599,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5875</v>
+        <v>0.5225</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-142</v>
+        <v>-109</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14561,7 +14631,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14578,7 +14648,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -14593,14 +14663,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4125</v>
+        <v>0.4775</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14625,7 +14695,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14637,17 +14707,17 @@
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14657,18 +14727,16 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4498198198198199</v>
+        <v>0.5875</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>122</v>
-      </c>
-      <c r="H69" s="15" t="n">
-        <v>122</v>
-      </c>
+        <v>-142</v>
+      </c>
+      <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
         <v/>
@@ -14691,7 +14759,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 58.8% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14703,17 +14771,17 @@
     <row r="70">
       <c r="A70" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14723,18 +14791,16 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.550209009009009</v>
+        <v>0.4125</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-122</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
         <v/>
@@ -14757,7 +14823,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 41.2% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14784,22 +14850,22 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5018365384615384</v>
+        <v>0.4506756756756757</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-101</v>
+        <v>122</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-108</v>
+        <v>122</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14823,7 +14889,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14850,22 +14916,22 @@
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4981952380952381</v>
+        <v>0.5493272727272728</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>101</v>
+        <v>-122</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14889,7 +14955,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14916,22 +14982,22 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4216521739130435</v>
+        <v>0.5022058823529412</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>137</v>
+        <v>-101</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14955,7 +15021,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14982,22 +15048,22 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5783627450980393</v>
+        <v>0.4978</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-137</v>
+        <v>101</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-155</v>
+        <v>100</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -15021,7 +15087,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15038,32 +15104,32 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3377777777777778</v>
+        <v>0.3887022900763358</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15087,7 +15153,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15104,32 +15170,32 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Pittsburgh Pirates +1.5</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6621814814814815</v>
+        <v>0.611278947368421</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-196</v>
+        <v>-157</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-170</v>
+        <v>-185</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15153,7 +15219,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15180,22 +15246,22 @@
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Over 6.5</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5506809523809523</v>
+        <v>0.3385555555555556</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-123</v>
+        <v>195</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-110</v>
+        <v>170</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15219,7 +15285,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15246,22 +15312,22 @@
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Under 6.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4493238095238095</v>
+        <v>0.6614259259259259</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>123</v>
+        <v>-195</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-110</v>
+        <v>-170</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -15285,7 +15351,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15312,22 +15378,22 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Over 7</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4975238095238095</v>
+        <v>0.50315</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>101</v>
+        <v>-101</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15351,7 +15417,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15378,22 +15444,22 @@
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds +1.5</t>
+          <t>Under 7</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5024782608695653</v>
+        <v>0.4968292682926829</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-130</v>
+        <v>105</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15417,7 +15483,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15434,32 +15500,32 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5527369369369369</v>
+        <v>0.4812608695652174</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-124</v>
+        <v>108</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-122</v>
+        <v>130</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15483,7 +15549,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15500,32 +15566,32 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Cincinnati Reds +1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4472687224669604</v>
+        <v>0.5187565217391304</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>124</v>
+        <v>-108</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>127</v>
+        <v>-130</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15549,7 +15615,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15566,12 +15632,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15581,17 +15647,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.54355</v>
+        <v>0.5460718894009216</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>100</v>
+        <v>-117</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15615,7 +15681,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15632,12 +15698,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15647,17 +15713,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.45645</v>
+        <v>0.453918918918919</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15681,7 +15747,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15698,12 +15764,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -15713,17 +15779,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4862910798122066</v>
+        <v>0.5445725490196078</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>106</v>
+        <v>-120</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15747,7 +15813,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15764,12 +15830,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -15779,17 +15845,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5136990610328639</v>
+        <v>0.4553921568627451</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-106</v>
+        <v>120</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15813,7 +15879,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15830,32 +15896,32 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5197064516129032</v>
+        <v>0.4741784037558686</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-108</v>
+        <v>111</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-117</v>
+        <v>113</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15879,7 +15945,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15896,32 +15962,32 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4803286384976526</v>
+        <v>0.5258195121951219</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>108</v>
+        <v>-111</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>113</v>
+        <v>-105</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15945,7 +16011,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15962,32 +16028,32 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4758064516129032</v>
+        <v>0.5762352941176471</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>110</v>
+        <v>-136</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>117</v>
+        <v>-155</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16011,7 +16077,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16028,32 +16094,32 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5241815668202765</v>
+        <v>0.4237551020408163</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-110</v>
+        <v>136</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-117</v>
+        <v>145</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16077,7 +16143,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16094,12 +16160,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -16109,17 +16175,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.406037037037037</v>
+        <v>0.4862910798122066</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16143,7 +16209,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16160,12 +16226,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -16175,17 +16241,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5939893536121673</v>
+        <v>0.5136990610328639</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-146</v>
+        <v>-106</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-163</v>
+        <v>-113</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16209,7 +16275,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16226,12 +16292,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -16241,17 +16307,17 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.425234375</v>
+        <v>0.5197064516129032</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>135</v>
+        <v>-108</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>156</v>
+        <v>-117</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16275,7 +16341,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 42.5% (fair +135). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16292,12 +16358,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -16307,17 +16373,17 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5747625000000001</v>
+        <v>0.4803286384976526</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-135</v>
+        <v>108</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-156</v>
+        <v>113</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16341,7 +16407,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 57.5% (fair -135). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16350,9 +16416,933 @@
         <v/>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>0.4721171171171172</v>
+      </c>
+      <c r="G95" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I95" s="13">
+        <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
+        <v/>
+      </c>
+      <c r="J95" s="16">
+        <f>IF($H$95="","",$F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))</f>
+        <v/>
+      </c>
+      <c r="K95" s="17">
+        <f>IF($H$95="","",MAX(0,($F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))/IF($H$95&lt;0,-100/$H$95,$H$95/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L95" s="18">
+        <f>IF($H$95="","",ROUND(MIN($K$95,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M95" s="12">
+        <f>IF($J$95="","",IF($J$95&lt;0,"Pass",IF($J$95&lt;'Settings'!$B$4,"Thin",IF($J$95&lt;0.06,"✅ Sharp band",IF($J$95&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N95" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.2% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O95" s="15" t="n"/>
+      <c r="P95" s="16">
+        <f>IF(OR($H$95="",$O$95=""),"",(1+IF($H$95&lt;0,-100/$H$95,$H$95/100))/(1+IF($O$95&lt;0,-100/$O$95,$O$95/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>0.5279018433179723</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I96" s="13">
+        <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
+        <v/>
+      </c>
+      <c r="J96" s="16">
+        <f>IF($H$96="","",$F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))</f>
+        <v/>
+      </c>
+      <c r="K96" s="17">
+        <f>IF($H$96="","",MAX(0,($F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))/IF($H$96&lt;0,-100/$H$96,$H$96/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L96" s="18">
+        <f>IF($H$96="","",ROUND(MIN($K$96,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M96" s="12">
+        <f>IF($J$96="","",IF($J$96&lt;0,"Pass",IF($J$96&lt;'Settings'!$B$4,"Thin",IF($J$96&lt;0.06,"✅ Sharp band",IF($J$96&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N96" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.8% (fair -112). Your call.</t>
+        </is>
+      </c>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="16">
+        <f>IF(OR($H$96="",$O$96=""),"",(1+IF($H$96&lt;0,-100/$H$96,$H$96/100))/(1+IF($O$96&lt;0,-100/$O$96,$O$96/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>0.5579</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="I97" s="13">
+        <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="16">
+        <f>IF($H$97="","",$F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF($H$97="","",MAX(0,($F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))/IF($H$97&lt;0,-100/$H$97,$H$97/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L97" s="18">
+        <f>IF($H$97="","",ROUND(MIN($K$97,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M97" s="12">
+        <f>IF($J$97="","",IF($J$97&lt;0,"Pass",IF($J$97&lt;'Settings'!$B$4,"Thin",IF($J$97&lt;0.06,"✅ Sharp band",IF($J$97&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.8% (fair -126). Your call.</t>
+        </is>
+      </c>
+      <c r="O97" s="15" t="n"/>
+      <c r="P97" s="16">
+        <f>IF(OR($H$97="",$O$97=""),"",(1+IF($H$97&lt;0,-100/$H$97,$H$97/100))/(1+IF($O$97&lt;0,-100/$O$97,$O$97/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I98" s="13">
+        <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>IF($H$98="","",$F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF($H$98="","",MAX(0,($F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))/IF($H$98&lt;0,-100/$H$98,$H$98/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L98" s="18">
+        <f>IF($H$98="","",ROUND(MIN($K$98,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M98" s="12">
+        <f>IF($J$98="","",IF($J$98&lt;0,"Pass",IF($J$98&lt;'Settings'!$B$4,"Thin",IF($J$98&lt;0.06,"✅ Sharp band",IF($J$98&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N98" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.2% (fair +126). Your call.</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="16">
+        <f>IF(OR($H$98="",$O$98=""),"",(1+IF($H$98&lt;0,-100/$H$98,$H$98/100))/(1+IF($O$98&lt;0,-100/$O$98,$O$98/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Texas Rangers -1.5</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>0.3680514705882353</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>172</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="I99" s="13">
+        <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="16">
+        <f>IF($H$99="","",$F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>IF($H$99="","",MAX(0,($F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))/IF($H$99&lt;0,-100/$H$99,$H$99/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L99" s="18">
+        <f>IF($H$99="","",ROUND(MIN($K$99,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M99" s="12">
+        <f>IF($J$99="","",IF($J$99&lt;0,"Pass",IF($J$99&lt;'Settings'!$B$4,"Thin",IF($J$99&lt;0.06,"✅ Sharp band",IF($J$99&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N99" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.8% (fair +172). Your call.</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="n"/>
+      <c r="P99" s="16">
+        <f>IF(OR($H$99="",$O$99=""),"",(1+IF($H$99&lt;0,-100/$H$99,$H$99/100))/(1+IF($O$99&lt;0,-100/$O$99,$O$99/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>Detroit Tigers +1.5</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>0.6319592592592592</v>
+      </c>
+      <c r="G100" s="14" t="n">
+        <v>-172</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>-170</v>
+      </c>
+      <c r="I100" s="13">
+        <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="16">
+        <f>IF($H$100="","",$F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF($H$100="","",MAX(0,($F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))/IF($H$100&lt;0,-100/$H$100,$H$100/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L100" s="18">
+        <f>IF($H$100="","",ROUND(MIN($K$100,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M100" s="12">
+        <f>IF($J$100="","",IF($J$100&lt;0,"Pass",IF($J$100&lt;'Settings'!$B$4,"Thin",IF($J$100&lt;0.06,"✅ Sharp band",IF($J$100&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.2% (fair -172). Your call.</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="16">
+        <f>IF(OR($H$100="",$O$100=""),"",(1+IF($H$100&lt;0,-100/$H$100,$H$100/100))/(1+IF($O$100&lt;0,-100/$O$100,$O$100/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.3977898550724638</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>151</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>176</v>
+      </c>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.8% (fair +151). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.6021906474820143</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>-151</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>-178</v>
+      </c>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.2% (fair -151). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Over 7.5</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.4851219512195122</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="I103" s="13">
+        <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="16">
+        <f>IF($H$103="","",$F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF($H$103="","",MAX(0,($F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))/IF($H$103&lt;0,-100/$H$103,$H$103/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>IF($H$103="","",ROUND(MIN($K$103,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M103" s="12">
+        <f>IF($J$103="","",IF($J$103&lt;0,"Pass",IF($J$103&lt;'Settings'!$B$4,"Thin",IF($J$103&lt;0.06,"✅ Sharp band",IF($J$103&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.5% (fair +106). Your call.</t>
+        </is>
+      </c>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="16">
+        <f>IF(OR($H$103="",$O$103=""),"",(1+IF($H$103&lt;0,-100/$H$103,$H$103/100))/(1+IF($O$103&lt;0,-100/$O$103,$O$103/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Under 7.5</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>0.5149047619047619</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>-106</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I104" s="13">
+        <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="16">
+        <f>IF($H$104="","",$F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF($H$104="","",MAX(0,($F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))/IF($H$104&lt;0,-100/$H$104,$H$104/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L104" s="18">
+        <f>IF($H$104="","",ROUND(MIN($K$104,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M104" s="12">
+        <f>IF($J$104="","",IF($J$104&lt;0,"Pass",IF($J$104&lt;'Settings'!$B$4,"Thin",IF($J$104&lt;0.06,"✅ Sharp band",IF($J$104&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.5% (fair -106). Your call.</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="16">
+        <f>IF(OR($H$104="",$O$104=""),"",(1+IF($H$104&lt;0,-100/$H$104,$H$104/100))/(1+IF($O$104&lt;0,-100/$O$104,$O$104/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Mariners -1.5</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>0.4307619047619047</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="I105" s="13">
+        <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>IF($H$105="","",$F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF($H$105="","",MAX(0,($F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))/IF($H$105&lt;0,-100/$H$105,$H$105/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>IF($H$105="","",ROUND(MIN($K$105,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M105" s="12">
+        <f>IF($J$105="","",IF($J$105&lt;0,"Pass",IF($J$105&lt;'Settings'!$B$4,"Thin",IF($J$105&lt;0.06,"✅ Sharp band",IF($J$105&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.1% (fair +132). Your call.</t>
+        </is>
+      </c>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="16">
+        <f>IF(OR($H$105="",$O$105=""),"",(1+IF($H$105&lt;0,-100/$H$105,$H$105/100))/(1+IF($O$105&lt;0,-100/$O$105,$O$105/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels +1.5</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.5692304347826088</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-130</v>
+      </c>
+      <c r="I106" s="13">
+        <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="16">
+        <f>IF($H$106="","",$F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF($H$106="","",MAX(0,($F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))/IF($H$106&lt;0,-100/$H$106,$H$106/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>IF($H$106="","",ROUND(MIN($K$106,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M106" s="12">
+        <f>IF($J$106="","",IF($J$106&lt;0,"Pass",IF($J$106&lt;'Settings'!$B$4,"Thin",IF($J$106&lt;0.06,"✅ Sharp band",IF($J$106&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.9% (fair -132). Your call.</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="16">
+        <f>IF(OR($H$106="",$O$106=""),"",(1+IF($H$106&lt;0,-100/$H$106,$H$106/100))/(1+IF($O$106&lt;0,-100/$O$106,$O$106/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.4226953125</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>137</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>156</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 42.3% (fair +137). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.5772609375000001</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>-137</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-156</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.7% (fair -137). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J94">
+  <conditionalFormatting sqref="J5:J108">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16518,13 +17508,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6433170278637771</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-148</v>
+        <v>-180</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-203</v>
+        <v>-223</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16548,7 +17538,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 59.6% (fair -148). Your call.</t>
+          <t>Model 64.3% (fair -180). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16584,13 +17574,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4037</v>
+        <v>0.356656346749226</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16614,7 +17604,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 40.4% (fair +148). Your call.</t>
+          <t>Model 35.7% (fair +180). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16650,13 +17640,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6154460093896714</v>
+        <v>0.6154411764705883</v>
       </c>
       <c r="G7" s="14" t="n">
         <v>-160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16722,7 +17712,7 @@
         <v>160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -17046,13 +18036,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4191079812206573</v>
+        <v>0.4191244239631337</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -17118,7 +18108,7 @@
         <v>-139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -17250,7 +18240,7 @@
         <v>147</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -17785,28 +18775,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C5" s="22" t="n">
         <v>0.2493</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.46</v>
+        <v>0.4577</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-0.77</v>
+        <v>-1.77</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.39</v>
+        <v>-0.88</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5028</v>
       </c>
     </row>
     <row r="6">
@@ -17816,28 +18806,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>0.2508</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4783</v>
+        <v>0.4753</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>1.88</v>
+        <v>0.88</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>1.17</v>
+        <v>0.54</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5203</v>
+        <v>0.5235</v>
       </c>
     </row>
     <row r="7">
@@ -17920,7 +18910,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=249, ECE 0.055 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=250, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -18034,16 +19024,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5443</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5161</v>
+        <v>0.5213</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0282</v>
+        <v>-0.0226</v>
       </c>
     </row>
     <row r="22">

--- a/data/output/workbook/2026-07-01.xlsx
+++ b/data/output/workbook/2026-07-01.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10315575"/>
+    <ext cx="10125075" cy="10734675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10544175"/>
+    <ext cx="10125075" cy="10315575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -521,7 +521,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10287000"/>
+    <ext cx="10125075" cy="9906000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 15:51</t>
+          <t>2026-07-01 17:27</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3927,883 +3927,883 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Toronto Blue Jays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F64" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G64" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H64" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I64" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J64" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K64" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L64" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M64" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N64" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O64" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P64" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q64" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>3.859</v>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr"/>
+      <c r="J65" s="36" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>4.452</v>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Toronto Blue Jays defense</t>
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>7.894</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B67" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C67" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D67" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E67" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F67" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G67" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H67" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I67" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J67" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K67" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L67" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M67" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N67" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O67" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P67" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q67" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="C67" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr"/>
+      <c r="J67" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B68" s="32" t="n">
-        <v>3.859</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="C68" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.75</v>
+      <c r="J68" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O68" s="32" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="P68" s="32" t="n">
-        <v>4.452</v>
+        <v>9.489000000000001</v>
       </c>
       <c r="Q68" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B72" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F72" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G72" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H72" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I72" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J72" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K72" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L72" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M72" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N72" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O72" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P72" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q72" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B69" s="32" t="n">
-        <v>7.306</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.894</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
+      <c r="B74" s="32" t="n">
+        <v>8.468</v>
+      </c>
+      <c r="C74" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>7.918</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B70" s="32" t="n">
-        <v>0.9389999999999999</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
+      <c r="B75" s="32" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B71" s="32" t="n">
-        <v>8.407999999999999</v>
-      </c>
-      <c r="C71" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>9.489000000000001</v>
-      </c>
-      <c r="Q71" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B72" s="32" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="C72" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D72" s="32" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E72" s="32" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="F72" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays offense vs New York Mets defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B75" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C75" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D75" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E75" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F75" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G75" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H75" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I75" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J75" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K75" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L75" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M75" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N75" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O75" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P75" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q75" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B76" s="32" t="n">
-        <v>4</v>
+        <v>7.298</v>
       </c>
       <c r="C76" s="32" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>6.4</v>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>5.45</v>
+      <c r="J76" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O76" s="32" t="n">
-        <v>4.767</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="P76" s="32" t="n">
-        <v>4.526</v>
+        <v>9.061</v>
       </c>
       <c r="Q76" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>8.468</v>
+        <v>0.431</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.267</v>
+      </c>
+      <c r="D77" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E77" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F77" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G77" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J77" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L77" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M77" s="32" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N77" s="32" t="n">
+        <v>0.85</v>
       </c>
       <c r="O77" s="32" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>7.918</v>
+        <v>0.514</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B78" s="32" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="C78" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q78" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="n">
-        <v>7.298</v>
-      </c>
-      <c r="C79" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="32" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="P79" s="32" t="n">
-        <v>9.061</v>
-      </c>
-      <c r="Q79" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B80" s="32" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="C80" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="D80" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E80" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F80" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G80" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H80" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L80" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M80" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N80" s="32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O80" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>0.514</v>
-      </c>
-      <c r="Q80" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7582,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7599,325 +7599,171 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J68" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>4.921</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>1.061</v>
+        <v>4.77</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.433</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>4.921</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.939</v>
+        <v>7.776</v>
       </c>
       <c r="C71" s="32" t="n">
         <v>9.199999999999999</v>
@@ -7974,402 +7820,402 @@
         </is>
       </c>
       <c r="O71" s="32" t="n">
-        <v>9</v>
+        <v>6.75</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.417</v>
+        <v>7.625</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.662</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H72" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J72" s="34" t="inlineStr">
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.635</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F75" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G75" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H75" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I75" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J75" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K75" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L75" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M75" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N75" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O75" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P75" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q75" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>4.882</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H76" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>6.033</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>5.162</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>8.083</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>1.417</v>
+        <v>4.882</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.633</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>6.033</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>5.162</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>7.729</v>
+        <v>8.083</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>9.25</v>
+        <v>7.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -8423,71 +8269,225 @@
         </is>
       </c>
       <c r="O79" s="32" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="P79" s="32" t="n">
-        <v>8.265000000000001</v>
+        <v>8.305999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B80" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="C80" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="D80" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E80" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F80" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G80" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="34" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="36" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="K80" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L80" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M80" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N80" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O80" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P80" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.595</v>
       </c>
-      <c r="Q80" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6154411764705883</v>
+        <v>0.6595285714285715</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-160</v>
+        <v>-194</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>104</v>
+        <v>-110</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8775,12 +8775,12 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings @ Connecticut Sun</t>
+          <t>Atlanta Dream @ Washington Mystics</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8790,17 +8790,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Connecticut Sun</t>
+          <t>Washington Mystics</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.2926</v>
+        <v>0.3369729729729729</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>242</v>
+        <v>197</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +242). Your call.</t>
+          <t>Model 33.7% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8841,12 +8841,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>Dallas Wings @ Connecticut Sun</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8856,17 +8856,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics</t>
+          <t>Connecticut Sun</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.356656346749226</v>
+        <v>0.293175</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +180). Your call.</t>
+          <t>Model 29.3% (fair +241). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8902,37 +8902,37 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4771244635193133</v>
+        <v>0.4813913043478261</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8973,32 +8973,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4812608695652174</v>
+        <v>0.3922340425531915</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9034,17 +9034,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3977898550724638</v>
+        <v>0.4744206008583691</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9105,32 +9105,32 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics +6.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5551764705882353</v>
+        <v>0.4268359375</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-125</v>
+        <v>134</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-104</v>
+        <v>156</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9171,32 +9171,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4226953125</v>
+        <v>0.54525</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>137</v>
+        <v>-120</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9256,13 +9256,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5369154228855721</v>
+        <v>0.53455</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9298,37 +9298,37 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5445725490196078</v>
+        <v>0.5224509803921569</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-120</v>
+        <v>-109</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9364,37 +9364,37 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5</v>
+        <v>0.447563025210084</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9430,37 +9430,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 170.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4411203319502074</v>
+        <v>0.5</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 50.0% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9496,37 +9496,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5209803921568628</v>
+        <v>0.5422784313725491</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-109</v>
+        <v>-118</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>-104</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9562,17 +9562,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4986854460093897</v>
+        <v>0.477972972972973</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9633,12 +9633,12 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4533905579399142</v>
+        <v>0.4488135593220338</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9699,32 +9699,32 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5160784313725489</v>
+        <v>0.4393360995850622</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-107</v>
+        <v>128</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9765,32 +9765,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Seattle Storm +5.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.6614259259259259</v>
+        <v>0.5188235294117647</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-195</v>
+        <v>-108</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-170</v>
+        <v>104</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9826,37 +9826,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4721171171171172</v>
+        <v>0.5602784037558686</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>112</v>
+        <v>-127</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>122</v>
+        <v>-113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9897,32 +9897,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Seattle Storm +5.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.6643222222222221</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-109</v>
+        <v>-198</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>100</v>
+        <v>-170</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 66.4% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9963,32 +9963,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4582378854625551</v>
+        <v>0.5167647058823529</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>118</v>
+        <v>-107</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10029,12 +10029,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -10044,17 +10044,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4684684684684685</v>
+        <v>0.4946478873239437</v>
       </c>
       <c r="G25" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="H25" s="15" t="n">
         <v>113</v>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>122</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +113). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10095,32 +10095,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5712567567567568</v>
+        <v>0.4671999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-133</v>
+        <v>114</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-122</v>
+        <v>125</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10176,17 +10176,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4237551020408163</v>
+        <v>0.3953231939163498</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10293,32 +10293,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5258195121951219</v>
+        <v>0.4773271889400922</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-111</v>
+        <v>109</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-105</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 47.7% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -10519,10 +10519,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4411203319502074</v>
+        <v>0.4393360995850622</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>141</v>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -10585,10 +10585,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5588852459016393</v>
+        <v>0.5606557377049181</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-127</v>
+        <v>-128</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-144</v>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10651,10 +10651,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4575</v>
+        <v>0.4602</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>116</v>
@@ -10681,7 +10681,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +119). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10717,10 +10717,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5425</v>
+        <v>0.5398000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-119</v>
+        <v>-117</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>101</v>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -119). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10783,10 +10783,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3816</v>
+        <v>0.3908</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>144</v>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10849,10 +10849,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6184000000000001</v>
+        <v>0.6092</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-162</v>
+        <v>-156</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>144</v>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10915,10 +10915,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4986854460093897</v>
+        <v>0.4946478873239437</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>113</v>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10981,10 +10981,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5013173076923076</v>
+        <v>0.5053673076923076</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-108</v>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5209803921568628</v>
+        <v>0.5224509803921569</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>-109</v>
@@ -11077,7 +11077,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.479</v>
+        <v>0.47755</v>
       </c>
       <c r="G14" s="14" t="n">
         <v>109</v>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11179,10 +11179,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3244</v>
+        <v>0.3366</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>175</v>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 32.4% (fair +208). Your call.</t>
+          <t>Model 33.7% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11245,10 +11245,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6756</v>
+        <v>0.6634</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-208</v>
+        <v>-197</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>186</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 67.6% (fair -208). Your call.</t>
+          <t>Model 66.3% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11311,10 +11311,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4636</v>
+        <v>0.4688</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>138</v>
@@ -11341,7 +11341,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 46.4% (fair +116). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5364</v>
+        <v>0.5312</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-116</v>
+        <v>-113</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>141</v>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.6% (fair -116). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4103</v>
+        <v>0.4215</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>116</v>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11509,10 +11509,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5897</v>
+        <v>0.5785</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-144</v>
+        <v>-137</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>101</v>
@@ -11539,7 +11539,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11575,10 +11575,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.41</v>
+        <v>0.402</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -11605,7 +11605,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11641,10 +11641,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5900000000000001</v>
+        <v>0.598</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-144</v>
+        <v>-149</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-106</v>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11707,10 +11707,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4579723502304148</v>
+        <v>0.4632718894009217</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>117</v>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 46.3% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11773,10 +11773,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5420281105990784</v>
+        <v>0.5367442396313364</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-118</v>
+        <v>-116</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-117</v>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 53.7% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4838940594059406</v>
+        <v>0.4832376237623762</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>107</v>
@@ -11869,7 +11869,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5160784313725489</v>
+        <v>0.5167647058823529</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>-107</v>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4117</v>
+        <v>0.398</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>163</v>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 39.8% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12037,10 +12037,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5883</v>
+        <v>0.602</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-143</v>
+        <v>-151</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 60.2% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12103,10 +12103,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4851184834123222</v>
+        <v>0.479478672985782</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>111</v>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5148611374407582</v>
+        <v>0.5204900473933649</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-106</v>
+        <v>-109</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-111</v>
@@ -12199,7 +12199,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.0% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12235,10 +12235,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.2371</v>
+        <v>0.2573</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 23.7% (fair +322). Your call.</t>
+          <t>Model 25.7% (fair +289). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12301,10 +12301,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.7629</v>
+        <v>0.7427</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-322</v>
+        <v>-289</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>113</v>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 76.3% (fair -322). Your call.</t>
+          <t>Model 74.3% (fair -289). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12367,10 +12367,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3641</v>
+        <v>0.38</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>163</v>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12433,10 +12433,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6359</v>
+        <v>0.62</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-175</v>
+        <v>-163</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>163</v>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12499,10 +12499,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4943203883495145</v>
+        <v>0.4934951456310679</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>106</v>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12565,10 +12565,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5056788461538461</v>
+        <v>0.5065096153846154</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-102</v>
+        <v>-103</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-108</v>
@@ -12595,7 +12595,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12631,10 +12631,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3994</v>
+        <v>0.3937</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>107</v>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12697,10 +12697,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6006</v>
+        <v>0.6063000000000001</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-150</v>
+        <v>-154</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>113</v>
@@ -12727,7 +12727,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12763,13 +12763,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4533905579399142</v>
+        <v>0.447563025210084</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12829,13 +12829,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5466128755364807</v>
+        <v>0.5524638655462184</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-121</v>
+        <v>-123</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12895,10 +12895,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5766</v>
+        <v>0.5746</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>108</v>
@@ -12925,7 +12925,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12961,10 +12961,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4234</v>
+        <v>0.4254</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>105</v>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13027,10 +13027,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3733</v>
+        <v>0.374</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>156</v>
@@ -13057,7 +13057,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 37.4% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13093,13 +13093,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6267</v>
+        <v>0.626</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-168</v>
+        <v>-167</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 62.6% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13159,13 +13159,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4684684684684685</v>
+        <v>0.4671999999999999</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +113). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13225,10 +13225,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5315243243243243</v>
+        <v>0.5327882882882883</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-113</v>
+        <v>-114</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>-122</v>
@@ -13255,7 +13255,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -113). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13291,10 +13291,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.444</v>
+        <v>0.4458</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>117</v>
@@ -13321,7 +13321,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13357,10 +13357,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.556</v>
+        <v>0.5542</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>105</v>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13423,13 +13423,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.3675</v>
+        <v>0.3623</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 36.2% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13489,10 +13489,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.6376999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-172</v>
+        <v>-176</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>-119</v>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 63.3% (fair -172). Your call.</t>
+          <t>Model 63.8% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13555,13 +13555,13 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5417920704845816</v>
+        <v>0.5511793991416309</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-118</v>
+        <v>-123</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13621,13 +13621,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4582378854625551</v>
+        <v>0.4488135593220338</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13651,7 +13651,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13687,13 +13687,13 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4631</v>
+        <v>0.4654</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13753,13 +13753,13 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5369154228855721</v>
+        <v>0.53455</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-116</v>
+        <v>-115</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.5712567567567568</v>
+        <v>0.5602784037558686</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13849,7 +13849,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 57.1% (fair -133). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13885,13 +13885,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.4287557603686636</v>
+        <v>0.4397619047619047</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13951,10 +13951,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.4771244635193133</v>
+        <v>0.4744206008583691</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>133</v>
@@ -13981,7 +13981,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14017,13 +14017,13 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5228819383259912</v>
+        <v>0.525553448275862</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-127</v>
+        <v>-132</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14079,17 +14079,17 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5759</v>
+        <v>0.474</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-136</v>
+        <v>111</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -14145,17 +14145,17 @@
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4241</v>
+        <v>0.526</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>136</v>
+        <v>-111</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>111</v>
+        <v>-104</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -14475,10 +14475,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6171</v>
+        <v>0.6078</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-161</v>
+        <v>-155</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 61.7% (fair -161). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -14539,10 +14539,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.3829</v>
+        <v>0.3922</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -14567,7 +14567,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 38.3% (fair +161). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -14603,10 +14603,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5225</v>
+        <v>0.5264</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14667,10 +14667,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4775</v>
+        <v>0.4736</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14859,10 +14859,10 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4506756756756757</v>
+        <v>0.4480630630630631</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H71" s="15" t="n">
         <v>122</v>
@@ -14889,7 +14889,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14925,13 +14925,13 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5493272727272728</v>
+        <v>0.5519444444444445</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14955,7 +14955,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14987,17 +14987,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.5022058823529412</v>
+        <v>0.5092</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>-101</v>
+        <v>-104</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15053,17 +15053,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.4978</v>
+        <v>0.4908</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -15087,7 +15087,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15123,13 +15123,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3887022900763358</v>
+        <v>0.3953231939163498</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15153,7 +15153,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15189,13 +15189,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.611278947368421</v>
+        <v>0.6046333333333334</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-157</v>
+        <v>-153</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-185</v>
+        <v>-170</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15255,13 +15255,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.3385555555555556</v>
+        <v>0.3356934306569342</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 33.9% (fair +195). Your call.</t>
+          <t>Model 33.6% (fair +198). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.6614259259259259</v>
+        <v>0.6643222222222221</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-195</v>
+        <v>-198</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-170</v>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 66.4% (fair -198). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15383,17 +15383,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.50315</v>
+        <v>0.534</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-101</v>
+        <v>-115</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15417,7 +15417,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15449,17 +15449,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4968292682926829</v>
+        <v>0.466</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15483,7 +15483,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15519,7 +15519,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4812608695652174</v>
+        <v>0.4813913043478261</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>108</v>
@@ -15585,13 +15585,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5187565217391304</v>
+        <v>0.5186429184549356</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>-108</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-130</v>
+        <v>-133</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -15651,7 +15651,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5460718894009216</v>
+        <v>0.5457483870967742</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>-120</v>
@@ -15717,7 +15717,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.453918918918919</v>
+        <v>0.4542342342342343</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>120</v>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5445725490196078</v>
+        <v>0.5422784313725491</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>-104</v>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15849,13 +15849,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4553921568627451</v>
+        <v>0.4577073170731708</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15879,7 +15879,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4741784037558686</v>
+        <v>0.5254</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>111</v>
+        <v>-111</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>113</v>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15981,13 +15981,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5258195121951219</v>
+        <v>0.4746</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-111</v>
+        <v>111</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -16011,7 +16011,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16047,10 +16047,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5762352941176471</v>
+        <v>0.5778764705882353</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>-155</v>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16113,10 +16113,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4237551020408163</v>
+        <v>0.4221224489795918</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>145</v>
@@ -16143,7 +16143,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16311,10 +16311,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5197064516129032</v>
+        <v>0.5226718894009217</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>-117</v>
@@ -16341,7 +16341,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.3% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16377,13 +16377,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4803286384976526</v>
+        <v>0.4773271889400922</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16407,7 +16407,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.7% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16443,10 +16443,10 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4721171171171172</v>
+        <v>0.477972972972973</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H95" s="15" t="n">
         <v>122</v>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16509,13 +16509,13 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5279018433179723</v>
+        <v>0.5220465116279071</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-112</v>
+        <v>-109</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-117</v>
+        <v>-115</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16571,17 +16571,17 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5579</v>
+        <v>0.54525</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-126</v>
+        <v>-120</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16637,17 +16637,17 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4421</v>
+        <v>0.4547450980392156</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16707,10 +16707,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.3680514705882353</v>
+        <v>0.3591176470588235</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>172</v>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +172). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16773,13 +16773,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.6319592592592592</v>
+        <v>0.640878947368421</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-172</v>
+        <v>-178</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-170</v>
+        <v>-185</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -172). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16839,13 +16839,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.3977898550724638</v>
+        <v>0.3922340425531915</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16869,7 +16869,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 39.8% (fair +151). Your call.</t>
+          <t>Model 39.2% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16905,13 +16905,13 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.6021906474820143</v>
+        <v>0.6077517482517483</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-151</v>
+        <v>-155</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-178</v>
+        <v>-186</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 60.2% (fair -151). Your call.</t>
+          <t>Model 60.8% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16971,13 +16971,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4851219512195122</v>
+        <v>0.4879326923076923</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17001,7 +17001,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5149047619047619</v>
+        <v>0.5120571428571429</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-106</v>
+        <v>-105</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>-110</v>
+        <v>-103</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17103,13 +17103,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4307619047619047</v>
+        <v>0.4314883720930233</v>
       </c>
       <c r="G105" s="14" t="n">
         <v>132</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17169,13 +17169,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5692304347826088</v>
+        <v>0.568509009009009</v>
       </c>
       <c r="G106" s="14" t="n">
         <v>-132</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-130</v>
+        <v>-122</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17235,10 +17235,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4226953125</v>
+        <v>0.4268359375</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>156</v>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 42.7% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17301,10 +17301,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5772609375000001</v>
+        <v>0.573178125</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-137</v>
+        <v>-134</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>-156</v>
@@ -17331,7 +17331,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.3% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17508,13 +17508,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6433170278637771</v>
+        <v>0.6630324324324325</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-180</v>
+        <v>-197</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-223</v>
+        <v>-270</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 64.3% (fair -180). Your call.</t>
+          <t>Model 66.3% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -17574,13 +17574,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.356656346749226</v>
+        <v>0.3369729729729729</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 35.7% (fair +180). Your call.</t>
+          <t>Model 33.7% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -17636,17 +17636,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 167.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6154411764705883</v>
+        <v>0.6595285714285715</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-160</v>
+        <v>-194</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>-110</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -17702,17 +17702,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 167.5</t>
+          <t>Under 165.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.3846000000000001</v>
+        <v>0.3405</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>-110</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 34.1% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -17772,13 +17772,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5551764705882353</v>
+        <v>0.6055</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-125</v>
+        <v>-153</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -17802,7 +17802,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 60.6% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4448</v>
+        <v>0.3945</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>100</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 39.4% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -17904,13 +17904,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7074295918367347</v>
+        <v>0.7068</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-242</v>
+        <v>-241</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-292</v>
+        <v>-285</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -242). Your call.</t>
+          <t>Model 70.7% (fair -241). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -17970,10 +17970,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2926</v>
+        <v>0.293175</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>300</v>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +242). Your call.</t>
+          <t>Model 29.3% (fair +241). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -18240,7 +18240,7 @@
         <v>147</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -18564,10 +18564,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4787</v>
+        <v>0.48115</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>100</v>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -18630,13 +18630,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.5188235294117647</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -18775,25 +18775,25 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2493</v>
+        <v>0.2496</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4577</v>
+        <v>0.4581</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-1.77</v>
+        <v>-1.73</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.88</v>
+        <v>-0.85</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.99</v>
+        <v>2.47</v>
       </c>
       <c r="I5" s="13" t="n">
         <v>0.5028</v>
@@ -18806,28 +18806,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2508</v>
+        <v>0.2511</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4753</v>
+        <v>0.4756</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>4.02</v>
+        <v>3.38</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5235</v>
+        <v>0.5232</v>
       </c>
     </row>
     <row r="7">
@@ -18910,7 +18910,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=250, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=254, ECE 0.054 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -19005,16 +19005,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4574</v>
+        <v>0.4575</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4545</v>
+        <v>0.4615</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0028</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="21">
@@ -19024,16 +19024,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5433</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5213</v>
+        <v>0.5155</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0226</v>
+        <v>-0.0278</v>
       </c>
     </row>
     <row r="22">
@@ -20149,7 +20149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20166,174 +20166,249 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Cleveland Guardians defense</t>
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B68" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D68" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E68" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H68" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I68" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J68" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K68" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L68" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M68" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N68" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O68" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P68" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q68" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>4.148</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J68" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>3.867</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B69" s="32" t="n">
-        <v>4.148</v>
+        <v>7.816</v>
       </c>
       <c r="C69" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H69" s="36" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>3.867</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.4</v>
+        <v>10.2</v>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O69" s="32" t="n">
-        <v>4.333</v>
+        <v>9.667</v>
       </c>
       <c r="P69" s="32" t="n">
-        <v>4.132</v>
+        <v>7.939</v>
       </c>
       <c r="Q69" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.816</v>
+        <v>1.041</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="D70" s="32" t="inlineStr">
         <is>
@@ -20386,29 +20461,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O70" s="32" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>7.939</v>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.041</v>
+        <v>8.592000000000001</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -20461,320 +20540,316 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O71" s="32" t="n">
+        <v>8.667</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>9.388</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.592000000000001</v>
+        <v>0.622</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.867</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.5</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>8.667</v>
+        <v>0.367</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>9.388</v>
+        <v>0.37</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B75" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D75" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E75" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F75" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I75" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J75" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K75" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L75" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M75" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N75" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O75" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P75" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q75" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>3.855</v>
+      </c>
+      <c r="C76" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H76" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr"/>
+      <c r="J76" s="33" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Texas Rangers defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B76" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C76" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D76" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E76" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H76" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I76" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J76" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K76" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L76" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M76" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N76" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O76" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P76" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q76" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="K76" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L76" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M76" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="N76" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="P76" s="32" t="n">
+        <v>4.111</v>
+      </c>
+      <c r="Q76" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B77" s="32" t="n">
-        <v>3.855</v>
+        <v>7.735</v>
       </c>
       <c r="C77" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H77" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>9.5</v>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5</v>
+      <c r="J77" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O77" s="32" t="n">
-        <v>4.433</v>
+        <v>8.6</v>
       </c>
       <c r="P77" s="32" t="n">
-        <v>4.111</v>
+        <v>7.673</v>
       </c>
       <c r="Q77" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>7.735</v>
+        <v>0.959</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>9.5</v>
+        <v>0.167</v>
       </c>
       <c r="D78" s="32" t="inlineStr">
         <is>
@@ -20827,29 +20902,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O78" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P78" s="32" t="n">
-        <v>7.673</v>
+      <c r="O78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>0.959</v>
+        <v>8</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>0.167</v>
+        <v>9.833</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -20902,155 +20981,76 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O79" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.571</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>8</v>
+        <v>0.521</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>9.833</v>
-      </c>
-      <c r="D80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I80" s="32" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.367</v>
+      </c>
+      <c r="D80" s="32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="F80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H80" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J80" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M80" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="N80" s="32" t="n">
+        <v>0.9</v>
       </c>
       <c r="O80" s="32" t="n">
-        <v>9.6</v>
+        <v>0.667</v>
       </c>
       <c r="P80" s="32" t="n">
-        <v>8.571</v>
+        <v>0.797</v>
       </c>
       <c r="Q80" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B81" s="32" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="C81" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="D81" s="32" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E81" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G81" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H81" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="I81" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J81" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K81" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L81" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M81" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="N81" s="32" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O81" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="P81" s="32" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="Q81" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-01.xlsx
+++ b/data/output/workbook/2026-07-01.xlsx
@@ -371,7 +371,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10506075"/>
+    <ext cx="10125075" cy="10734675"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10048875"/>
+    <ext cx="10125075" cy="10696575"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-01 19:13</t>
+          <t>2026-07-01 22:52</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2091,419 +2091,127 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs New York Yankees defense</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D65" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E65" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F65" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G65" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H65" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I65" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J65" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K65" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L65" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M65" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N65" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O65" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P65" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q65" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>4.288</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>4.433</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>7.755</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="D67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>7.609</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="D68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P68" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>8.305999999999999</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>8.167</v>
-      </c>
-      <c r="D69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>8.435</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.5620000000000001</v>
+        <v>4.288</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>0.5669999999999999</v>
+        <v>4.767</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>0.55</v>
+        <v>5</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>0.533</v>
+        <v>4.8</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H70" s="33" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr">
@@ -2513,469 +2221,761 @@
       </c>
       <c r="J70" s="34" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="K70" s="32" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="L70" s="32" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="M70" s="32" t="n">
-        <v>0.533</v>
+        <v>4.867</v>
       </c>
       <c r="N70" s="32" t="n">
-        <v>0.6</v>
+        <v>4.55</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>0.6</v>
+        <v>4.433</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>0.479</v>
+        <v>3.737</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp 1st Inn R/G</t>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>7.755</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr"/>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.609</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Detroit Tigers defense</t>
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B73" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C73" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D73" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E73" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F73" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G73" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H73" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I73" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J73" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K73" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L73" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M73" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N73" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O73" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P73" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q73" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.305999999999999</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.435</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>4.776</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>4.733</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>4.2</v>
+        <v>0.55</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>3.8</v>
+        <v>0.533</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
+        <v>1</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>3.533</v>
+        <v>0.533</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>3.45</v>
+        <v>0.6</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>3.986</v>
+        <v>0.479</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>8.109</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="D75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>7.592</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P76" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>9.130000000000001</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="D77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>7.776</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>0.634</v>
+        <v>4.776</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>0.433</v>
+        <v>4.733</v>
       </c>
       <c r="D78" s="32" t="n">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="E78" s="32" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="F78" s="32" t="n">
-        <v>0.3</v>
+        <v>2.7</v>
       </c>
       <c r="G78" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>2.4</v>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I78" s="32" t="inlineStr"/>
       <c r="J78" s="36" t="inlineStr">
         <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O78" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P78" s="32" t="n">
+        <v>3.986</v>
+      </c>
+      <c r="Q78" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>8.109</v>
+      </c>
+      <c r="C79" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr"/>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>7.592</v>
+      </c>
+      <c r="Q79" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="31" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="C80" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr"/>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>7.776</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="C82" s="32" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="D82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E82" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F82" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H82" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
+        <is>
           <t>11th</t>
         </is>
       </c>
-      <c r="K78" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="L78" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M78" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N78" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="O78" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="P78" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q78" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7582,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7599,249 +7599,174 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Minnesota Twins offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D68" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E68" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F68" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G68" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H68" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I68" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J68" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K68" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L68" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M68" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N68" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O68" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P68" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q68" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>5.867</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>4.767</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>4.921</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>7.776</v>
+        <v>4.77</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5.433</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>5.867</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>4.9</v>
       </c>
       <c r="O70" s="32" t="n">
-        <v>6.75</v>
+        <v>4.767</v>
       </c>
       <c r="P70" s="32" t="n">
-        <v>7.625</v>
+        <v>4.921</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>1.061</v>
+        <v>7.776</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D71" s="32" t="inlineStr">
         <is>
@@ -7894,33 +7819,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O71" s="32" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>7.625</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>8.939</v>
+        <v>1.061</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="D72" s="32" t="inlineStr">
         <is>
@@ -7973,324 +7894,328 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O72" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>8.417</v>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.939</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.417</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B73" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.662</v>
       </c>
-      <c r="C73" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.767</v>
       </c>
-      <c r="D73" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="F73" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.9</v>
       </c>
-      <c r="G73" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>1.2</v>
       </c>
-      <c r="H73" s="33" t="inlineStr">
+      <c r="H74" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="I73" s="32" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J73" s="34" t="inlineStr">
+      <c r="J74" s="34" t="inlineStr">
         <is>
           <t>21st</t>
         </is>
       </c>
-      <c r="K73" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L73" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M73" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N73" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.75</v>
       </c>
-      <c r="O73" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P73" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.635</v>
       </c>
-      <c r="Q73" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Minnesota Twins defense</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C77" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E77" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F76" s="30" t="inlineStr">
+      <c r="F77" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G76" s="30" t="inlineStr">
+      <c r="G77" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H76" s="30" t="inlineStr">
+      <c r="H77" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I76" s="30" t="inlineStr">
+      <c r="I77" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J76" s="30" t="inlineStr">
+      <c r="J77" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K76" s="30" t="inlineStr">
+      <c r="K77" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L76" s="30" t="inlineStr">
+      <c r="L77" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M76" s="30" t="inlineStr">
+      <c r="M77" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N76" s="30" t="inlineStr">
+      <c r="N77" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O76" s="30" t="inlineStr">
+      <c r="O77" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P76" s="30" t="inlineStr">
+      <c r="P77" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q76" s="30" t="inlineStr">
+      <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>4.882</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H77" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J77" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>6.033</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>5.162</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B78" s="32" t="n">
-        <v>8.083</v>
+        <v>4.882</v>
       </c>
       <c r="C78" s="32" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="32" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.633</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E78" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L78" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M78" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N78" s="32" t="n">
+        <v>5.9</v>
       </c>
       <c r="O78" s="32" t="n">
-        <v>10</v>
+        <v>6.033</v>
       </c>
       <c r="P78" s="32" t="n">
-        <v>8.305999999999999</v>
+        <v>5.162</v>
       </c>
       <c r="Q78" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="32" t="n">
-        <v>1.417</v>
+        <v>8.083</v>
       </c>
       <c r="C79" s="32" t="n">
-        <v>1</v>
+        <v>7.25</v>
       </c>
       <c r="D79" s="32" t="inlineStr">
         <is>
@@ -8343,33 +8268,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P79" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O79" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P79" s="32" t="n">
+        <v>8.305999999999999</v>
       </c>
       <c r="Q79" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="32" t="n">
-        <v>7.729</v>
+        <v>1.417</v>
       </c>
       <c r="C80" s="32" t="n">
-        <v>9.25</v>
+        <v>1</v>
       </c>
       <c r="D80" s="32" t="inlineStr">
         <is>
@@ -8422,72 +8343,151 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O80" s="32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="P80" s="32" t="n">
-        <v>8.265000000000001</v>
+      <c r="O80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q80" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>7.729</v>
+      </c>
+      <c r="C81" s="32" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr"/>
+      <c r="J81" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P81" s="32" t="n">
+        <v>8.265000000000001</v>
+      </c>
+      <c r="Q81" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B81" s="32" t="n">
+      <c r="B82" s="32" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="C81" s="32" t="n">
+      <c r="C82" s="32" t="n">
         <v>0.667</v>
       </c>
-      <c r="D81" s="32" t="n">
+      <c r="D82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="E81" s="32" t="n">
+      <c r="E82" s="32" t="n">
         <v>0.333</v>
       </c>
-      <c r="F81" s="32" t="n">
+      <c r="F82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G81" s="32" t="n">
+      <c r="G82" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="34" t="inlineStr">
+      <c r="H82" s="34" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr"/>
-      <c r="J81" s="36" t="inlineStr">
+      <c r="I82" s="32" t="inlineStr"/>
+      <c r="J82" s="36" t="inlineStr">
         <is>
           <t>15th</t>
         </is>
       </c>
-      <c r="K81" s="32" t="n">
+      <c r="K82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="L81" s="32" t="n">
+      <c r="L82" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="M81" s="32" t="n">
+      <c r="M82" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N81" s="32" t="n">
+      <c r="N82" s="32" t="n">
         <v>0.45</v>
       </c>
-      <c r="O81" s="32" t="n">
+      <c r="O82" s="32" t="n">
         <v>0.7</v>
       </c>
-      <c r="P81" s="32" t="n">
+      <c r="P82" s="32" t="n">
         <v>0.595</v>
       </c>
-      <c r="Q81" s="35" t="inlineStr">
+      <c r="Q82" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8584,7 +8584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3453913043478261</v>
+        <v>0.3467826086956521</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>245</v>
@@ -8824,7 +8824,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8860,13 +8860,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.293175</v>
+        <v>0.2884146341463415</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +241). Your call.</t>
+          <t>Model 28.8% (fair +247). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8907,32 +8907,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Dream @ Washington Mystics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Washington Mystics +6.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5478846153846153</v>
+        <v>0.39</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-121</v>
+        <v>156</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8968,37 +8968,37 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4813913043478261</v>
+        <v>0.4680672268907564</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9022,7 +9022,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -9039,12 +9039,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9054,17 +9054,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3922340425531915</v>
+        <v>0.3996402877697841</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -9100,37 +9100,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Seattle Storm @ Phoenix Mercury</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4739055793991416</v>
+        <v>0.5234615384615384</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>111</v>
+        <v>-110</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -9166,37 +9166,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4116165413533834</v>
+        <v>0.5256372549019608</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>143</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -9237,12 +9237,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5353233830845772</v>
+        <v>0.5250980392156862</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-115</v>
+        <v>-111</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -9303,32 +9303,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5244607843137256</v>
+        <v>0.4455042016806723</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-110</v>
+        <v>124</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -9364,17 +9364,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5448274509803921</v>
+        <v>0.444873949579832</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-120</v>
+        <v>125</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-104</v>
+        <v>138</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -9430,37 +9430,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm @ Phoenix Mercury</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4387966804979253</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4471848739495798</v>
+        <v>0.495774647887324</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -9562,37 +9562,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5208823529411765</v>
+        <v>0.5473730769230769</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-109</v>
+        <v>-121</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9628,37 +9628,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4393360995850622</v>
+        <v>0.5267074626865672</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>128</v>
+        <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>141</v>
+        <v>-101</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9694,37 +9694,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4494893617021277</v>
+        <v>0.5633253456221198</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>122</v>
+        <v>-129</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>135</v>
+        <v>-117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +122). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9760,17 +9760,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9780,17 +9780,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.493849765258216</v>
+        <v>0.4788532110091744</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9826,17 +9826,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays @ Kansas City Royals</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9846,17 +9846,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4736486486486488</v>
+        <v>0.478256880733945</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9897,12 +9897,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9912,17 +9912,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Under 12.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5366780487804879</v>
+        <v>0.5075980392156864</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-116</v>
+        <v>-103</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-105</v>
+        <v>104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9958,17 +9958,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9978,17 +9978,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4712612612612613</v>
+        <v>0.6729818181818181</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>112</v>
+        <v>-206</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>122</v>
+        <v>-186</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 67.3% (fair -206). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -10024,37 +10024,37 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5639184331797235</v>
+        <v>0.5359499999999999</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-129</v>
+        <v>-115</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -10095,32 +10095,32 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Chicago White Sox @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6668597122302159</v>
+        <v>0.5054901960784313</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-200</v>
+        <v>-102</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-178</v>
+        <v>104</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 66.7% (fair -200). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -10161,12 +10161,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -10176,17 +10176,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.47963133640553</v>
+        <v>0.4908173076923076</v>
       </c>
       <c r="G27" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="H27" s="15" t="n">
         <v>108</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>117</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -10219,141 +10219,9 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>22:40</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Chicago White Sox -1.5</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>0.4224081632653061</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>137</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>145</v>
-      </c>
-      <c r="I28" s="13">
-        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
-        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L28" s="18">
-        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
-        </is>
-      </c>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="16">
-        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>00:05</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Over 8</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>0.5219512315270936</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>-109</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I29" s="13">
-        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
-        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L29" s="18">
-        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M29" s="12">
-        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="inlineStr">
-        <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
-        </is>
-      </c>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="16">
-        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J29">
+  <conditionalFormatting sqref="J5:J27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -10375,7 +10243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10519,7 +10387,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4393360995850622</v>
+        <v>0.4387966804979253</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>128</v>
@@ -10585,7 +10453,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.5606557377049181</v>
+        <v>0.5611868852459017</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>-128</v>
@@ -10651,10 +10519,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4602</v>
+        <v>0.45</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>116</v>
@@ -10681,7 +10549,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 46.0% (fair +117). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10717,10 +10585,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-117</v>
+        <v>-122</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>101</v>
@@ -10747,7 +10615,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.0% (fair -117). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10783,10 +10651,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3908</v>
+        <v>0.388</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>144</v>
@@ -10813,7 +10681,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10849,10 +10717,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.6092</v>
+        <v>0.612</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-156</v>
+        <v>-158</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>144</v>
@@ -10879,7 +10747,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10915,7 +10783,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.493849765258216</v>
+        <v>0.495774647887324</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>102</v>
@@ -10945,7 +10813,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10981,7 +10849,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5061461538461538</v>
+        <v>0.5042249999999999</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-102</v>
@@ -11011,7 +10879,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -11047,10 +10915,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5244607843137256</v>
+        <v>0.5256372549019608</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>104</v>
@@ -11077,7 +10945,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -11113,10 +10981,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.47555</v>
+        <v>0.47435</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>100</v>
@@ -11143,7 +11011,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -11179,10 +11047,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.3358</v>
+        <v>0.3368</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>175</v>
@@ -11209,7 +11077,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 33.6% (fair +198). Your call.</t>
+          <t>Model 33.7% (fair +197). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -11245,10 +11113,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.6642</v>
+        <v>0.6632</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-198</v>
+        <v>-197</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>186</v>
@@ -11275,7 +11143,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 66.4% (fair -198). Your call.</t>
+          <t>Model 66.3% (fair -197). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -11311,10 +11179,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.48</v>
+        <v>0.4843</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>138</v>
@@ -11341,7 +11209,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.4% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -11377,10 +11245,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.52</v>
+        <v>0.5157</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>141</v>
@@ -11407,7 +11275,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.6% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -11443,10 +11311,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.436</v>
+        <v>0.4309</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>116</v>
@@ -11473,7 +11341,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -11509,10 +11377,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5640000000000001</v>
+        <v>0.5690999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>101</v>
@@ -11539,7 +11407,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11575,10 +11443,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3935</v>
+        <v>0.389</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>144</v>
@@ -11605,7 +11473,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 39.4% (fair +154). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11641,10 +11509,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6065</v>
+        <v>0.611</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-154</v>
+        <v>-157</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-106</v>
@@ -11671,7 +11539,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -154). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11707,7 +11575,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4666820276497696</v>
+        <v>0.4668202764976958</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>114</v>
@@ -11773,7 +11641,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5332935483870967</v>
+        <v>0.5331857142857143</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-114</v>
@@ -11839,10 +11707,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4790970297029702</v>
+        <v>0.4749059405940594</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>-102</v>
@@ -11869,7 +11737,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.5% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11905,10 +11773,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5208823529411765</v>
+        <v>0.5250980392156862</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>104</v>
@@ -11935,7 +11803,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.5% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11971,10 +11839,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3896</v>
+        <v>0.3871</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>163</v>
@@ -12001,7 +11869,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -12037,10 +11905,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6129</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-157</v>
+        <v>-158</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-127</v>
@@ -12067,7 +11935,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -157). Your call.</t>
+          <t>Model 61.3% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -12103,10 +11971,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4700473933649288</v>
+        <v>0.4714691943127962</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>111</v>
@@ -12133,7 +12001,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -12169,10 +12037,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5299592417061612</v>
+        <v>0.5285388625592417</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-111</v>
@@ -12199,7 +12067,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12235,10 +12103,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.2823</v>
+        <v>0.2791</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>113</v>
@@ -12265,7 +12133,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 28.2% (fair +254). Your call.</t>
+          <t>Model 27.9% (fair +258). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -12301,10 +12169,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.7177</v>
+        <v>0.7209</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-254</v>
+        <v>-258</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>113</v>
@@ -12331,7 +12199,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 71.8% (fair -254). Your call.</t>
+          <t>Model 72.1% (fair -258). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12367,10 +12235,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.4016</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>163</v>
@@ -12397,7 +12265,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 40.2% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -12433,10 +12301,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.5984</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-144</v>
+        <v>-149</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>163</v>
@@ -12463,7 +12331,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 59.8% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -12499,10 +12367,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4878640776699029</v>
+        <v>0.4864563106796116</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>106</v>
@@ -12529,7 +12397,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -12565,10 +12433,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5121173076923077</v>
+        <v>0.5135711538461538</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-105</v>
+        <v>-106</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>-108</v>
@@ -12595,7 +12463,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12631,10 +12499,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.3961</v>
+        <v>0.3781</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>107</v>
@@ -12661,7 +12529,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 39.6% (fair +152). Your call.</t>
+          <t>Model 37.8% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -12697,10 +12565,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.6039</v>
+        <v>0.6219</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-152</v>
+        <v>-164</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>113</v>
@@ -12727,7 +12595,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 60.4% (fair -152). Your call.</t>
+          <t>Model 62.2% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12763,7 +12631,7 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4471848739495798</v>
+        <v>0.4455042016806723</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>124</v>
@@ -12793,7 +12661,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12829,7 +12697,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5528117647058823</v>
+        <v>0.5544932773109243</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>-124</v>
@@ -12859,7 +12727,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12895,10 +12763,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5677</v>
+        <v>0.5707</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-131</v>
+        <v>-133</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>108</v>
@@ -12925,7 +12793,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 56.8% (fair -131). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12961,10 +12829,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.4323</v>
+        <v>0.4293</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>105</v>
@@ -12991,7 +12859,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 43.2% (fair +131). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -13027,10 +12895,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3724</v>
+        <v>0.375</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>150</v>
@@ -13057,7 +12925,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 37.2% (fair +169). Your call.</t>
+          <t>Model 37.5% (fair +167). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -13093,10 +12961,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6275999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-169</v>
+        <v>-167</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>-108</v>
@@ -13123,7 +12991,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 62.5% (fair -167). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -13159,13 +13027,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4712612612612613</v>
+        <v>0.478256880733945</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -13189,7 +13057,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -13225,13 +13093,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5287090909090909</v>
+        <v>0.5217440366972477</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-112</v>
+        <v>-109</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -13255,7 +13123,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -13291,10 +13159,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4369</v>
+        <v>0.3905</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>117</v>
@@ -13321,7 +13189,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 39.1% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -13357,13 +13225,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5630999999999999</v>
+        <v>0.6094999999999999</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-129</v>
+        <v>-156</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -13387,7 +13255,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 60.9% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -13423,10 +13291,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.36</v>
+        <v>0.3522</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>163</v>
@@ -13453,7 +13321,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 36.0% (fair +178). Your call.</t>
+          <t>Model 35.2% (fair +184). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -13489,13 +13357,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.64</v>
+        <v>0.6477999999999999</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-178</v>
+        <v>-184</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -13519,7 +13387,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 64.0% (fair -178). Your call.</t>
+          <t>Model 64.8% (fair -184). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -13555,10 +13423,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5504944206008584</v>
+        <v>0.5551180257510729</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>-133</v>
@@ -13585,7 +13453,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13621,13 +13489,13 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4494893617021277</v>
+        <v>0.444873949579832</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13651,7 +13519,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +122). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13683,17 +13551,17 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 10.5</t>
+          <t>Over 11</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4647059405940594</v>
+        <v>0.3088</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>-102</v>
+        <v>122</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13717,7 +13585,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 30.9% (fair +224). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13749,17 +13617,17 @@
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Under 11</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5353233830845772</v>
+        <v>0.6912</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-115</v>
+        <v>-224</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13783,7 +13651,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 69.1% (fair -224). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13819,13 +13687,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4739055793991416</v>
+        <v>0.4680672268907564</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13849,7 +13717,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13885,13 +13753,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5260635193133048</v>
+        <v>0.5319378151260504</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-111</v>
+        <v>-114</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13915,7 +13783,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13947,17 +13815,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.474</v>
+        <v>0.5359499999999999</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>111</v>
+        <v>-115</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>125</v>
+        <v>-108</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13981,7 +13849,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 53.6% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -14013,17 +13881,17 @@
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.526</v>
+        <v>0.4640686274509804</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-111</v>
+        <v>115</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -14047,7 +13915,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 46.4% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -14089,7 +13957,7 @@
         <v>209</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14155,7 +14023,7 @@
         <v>-209</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-113</v>
+        <v>-109</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -14599,7 +14467,7 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5875</v>
+        <v>0.5867</v>
       </c>
       <c r="G67" s="14" t="n">
         <v>-142</v>
@@ -14627,7 +14495,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -142). Your call.</t>
+          <t>Model 58.7% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14663,7 +14531,7 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4125</v>
+        <v>0.4133</v>
       </c>
       <c r="G68" s="14" t="n">
         <v>142</v>
@@ -14691,7 +14559,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +142). Your call.</t>
+          <t>Model 41.3% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14727,10 +14595,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4498198198198199</v>
+        <v>0.4476576576576577</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H69" s="15" t="n">
         <v>122</v>
@@ -14757,7 +14625,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 44.8% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14793,10 +14661,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.550209009009009</v>
+        <v>0.5523522522522523</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="H70" s="15" t="n">
         <v>-122</v>
@@ -14823,7 +14691,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 55.2% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14855,17 +14723,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5823</v>
+        <v>0.5319</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-139</v>
+        <v>-114</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14889,7 +14757,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 58.2% (fair -139). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14921,17 +14789,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4177</v>
+        <v>0.4681</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14955,7 +14823,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 41.8% (fair +139). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14991,10 +14859,10 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4303</v>
+        <v>0.4364</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H73" s="15" t="n">
         <v>163</v>
@@ -15021,7 +14889,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -15057,13 +14925,13 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5697</v>
+        <v>0.5636</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-132</v>
+        <v>-129</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -15087,7 +14955,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -15123,13 +14991,13 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3331386861313869</v>
+        <v>0.3270503597122302</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -15153,7 +15021,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 33.3% (fair +200). Your call.</t>
+          <t>Model 32.7% (fair +206). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -15189,13 +15057,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6668597122302159</v>
+        <v>0.6729818181818181</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-200</v>
+        <v>-206</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-178</v>
+        <v>-186</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -15219,7 +15087,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 66.7% (fair -200). Your call.</t>
+          <t>Model 67.3% (fair -206). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -15255,13 +15123,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.534</v>
+        <v>0.5416</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -15285,7 +15153,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -15321,10 +15189,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.466</v>
+        <v>0.4584</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>113</v>
@@ -15351,7 +15219,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -15387,13 +15255,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4813913043478261</v>
+        <v>0.5774</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>108</v>
+        <v>-137</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -15417,7 +15285,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -15453,13 +15321,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5186429184549356</v>
+        <v>0.4226</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-108</v>
+        <v>137</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-133</v>
+        <v>117</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -15483,7 +15351,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -15519,13 +15387,13 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5439818181818181</v>
+        <v>0.5410576036866359</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-119</v>
+        <v>-118</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -15549,7 +15417,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -15585,10 +15453,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.456036866359447</v>
+        <v>0.4589861751152074</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>117</v>
@@ -15615,7 +15483,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15651,13 +15519,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4633</v>
+        <v>0.3644</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15681,7 +15549,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 46.3% (fair +116). Your call.</t>
+          <t>Model 36.4% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15717,10 +15585,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5366780487804879</v>
+        <v>0.6355999999999999</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-116</v>
+        <v>-174</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>-105</v>
@@ -15747,7 +15615,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 53.7% (fair -116). Your call.</t>
+          <t>Model 63.6% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15783,10 +15651,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5559478260869566</v>
+        <v>0.5617695652173913</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>-130</v>
@@ -15813,7 +15681,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 55.6% (fair -125). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15849,13 +15717,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.444046511627907</v>
+        <v>0.4381981981981982</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15879,7 +15747,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 44.4% (fair +125). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15915,13 +15783,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5448274509803921</v>
+        <v>0.5473730769230769</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-120</v>
+        <v>-121</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15945,7 +15813,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15981,10 +15849,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4551923076923077</v>
+        <v>0.4525961538461538</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>108</v>
@@ -16011,7 +15879,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -16047,13 +15915,13 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5252</v>
+        <v>0.4945</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-111</v>
+        <v>102</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -16077,7 +15945,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -16113,13 +15981,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4748</v>
+        <v>0.5054901960784313</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>111</v>
+        <v>-102</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -16143,7 +16011,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -16160,32 +16028,32 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5775725490196079</v>
+        <v>0.4908173076923076</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>-137</v>
+        <v>104</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-155</v>
+        <v>108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -16209,7 +16077,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -16226,32 +16094,32 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Cleveland Guardians</t>
+          <t>St. Louis Cardinals @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4224081632653061</v>
+        <v>0.5091428571428571</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>137</v>
+        <v>-104</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>145</v>
+        <v>-110</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -16275,7 +16143,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -16302,22 +16170,22 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4922115384615385</v>
+        <v>0.3499</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -16341,7 +16209,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -16368,22 +16236,22 @@
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5077809523809523</v>
+        <v>0.6501</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-103</v>
+        <v>-186</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-110</v>
+        <v>110</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -16407,7 +16275,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16434,22 +16302,22 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4109</v>
+        <v>0.3439</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
@@ -16473,7 +16341,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -16500,22 +16368,22 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>St. Louis Cardinals +1.5</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.5891</v>
+        <v>0.6561</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>-143</v>
+        <v>-191</v>
       </c>
       <c r="H96" s="15" t="n">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
@@ -16539,7 +16407,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -16556,32 +16424,32 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves +1.5</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.6221842105263158</v>
+        <v>0.5211904761904762</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-165</v>
+        <v>-109</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-185</v>
+        <v>-110</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -16605,7 +16473,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16622,32 +16490,32 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals @ Atlanta Braves</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.3778039215686275</v>
+        <v>0.4788262910798122</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -16671,7 +16539,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16698,22 +16566,22 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5263921658986175</v>
+        <v>0.5075980392156864</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-111</v>
+        <v>-103</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -16737,7 +16605,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16764,22 +16632,22 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4736486486486488</v>
+        <v>0.4924019607843137</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16803,7 +16671,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16820,32 +16688,32 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Kansas City Royals -1.5</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.47963133640553</v>
+        <v>0.3733</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>108</v>
+        <v>168</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16869,7 +16737,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16886,32 +16754,32 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ Texas Rangers</t>
+          <t>Tampa Bay Rays @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Tampa Bay Rays +1.5</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5204073732718895</v>
+        <v>0.6267</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-109</v>
+        <v>-168</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>-117</v>
+        <v>140</v>
       </c>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
@@ -16935,7 +16803,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -109). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16962,22 +16830,22 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5219512315270936</v>
+        <v>0.4788532110091744</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-109</v>
+        <v>109</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>-103</v>
+        <v>118</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -17001,7 +16869,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -17028,22 +16896,22 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.47805</v>
+        <v>0.5211082949308755</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>109</v>
+        <v>-109</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>100</v>
+        <v>-117</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -17067,7 +16935,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -17094,22 +16962,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.3563669064748201</v>
+        <v>0.5267074626865672</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>181</v>
+        <v>-111</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>178</v>
+        <v>-101</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -17133,7 +17001,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -17160,22 +17028,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers +1.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.6436052631578948</v>
+        <v>0.4732692307692308</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-181</v>
+        <v>111</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-185</v>
+        <v>108</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -17199,7 +17067,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -17216,32 +17084,32 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.3922340425531915</v>
+        <v>0.356</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="H107" s="15" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
@@ -17265,7 +17133,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 39.2% (fair +155). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -17282,32 +17150,32 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Detroit Tigers @ Texas Rangers</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Detroit Tigers +1.5</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.6077517482517483</v>
+        <v>0.644</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-155</v>
+        <v>-181</v>
       </c>
       <c r="H108" s="15" t="n">
-        <v>-186</v>
+        <v>-130</v>
       </c>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
@@ -17331,7 +17199,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 60.8% (fair -155). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -17358,22 +17226,22 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4841826923076923</v>
+        <v>0.39</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="H109" s="15" t="n">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="I109" s="13">
         <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
@@ -17397,7 +17265,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -17424,22 +17292,22 @@
       </c>
       <c r="D110" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5158038461538461</v>
+        <v>0.610027972027972</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-107</v>
+        <v>-156</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-108</v>
+        <v>-186</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -17463,7 +17331,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -17490,22 +17358,22 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners -1.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.4361032863849766</v>
+        <v>0.4953</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -17529,7 +17397,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -17556,22 +17424,22 @@
       </c>
       <c r="D112" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.5639184331797235</v>
+        <v>0.5046999999999999</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-129</v>
+        <v>-102</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>-117</v>
+        <v>125</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -17595,7 +17463,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17612,32 +17480,32 @@
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Seattle Mariners -1.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4116165413533834</v>
+        <v>0.4366511627906977</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17661,7 +17529,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17678,32 +17546,32 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Los Angeles Dodgers</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5883494296577947</v>
+        <v>0.5633253456221198</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-143</v>
+        <v>-129</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-163</v>
+        <v>-117</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17727,7 +17595,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 58.8% (fair -143). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17754,22 +17622,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.4896571428571428</v>
+        <v>0.3996402877697841</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-110</v>
+        <v>178</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -17793,7 +17661,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 49.0% (fair +104). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17820,22 +17688,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5103512195121951</v>
+        <v>0.6003338129496403</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-105</v>
+        <v>-178</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17859,7 +17727,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 51.0% (fair -104). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17886,22 +17754,22 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4415384615384615</v>
+        <v>0.5493</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>126</v>
+        <v>-122</v>
       </c>
       <c r="H117" s="15" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="I117" s="13">
         <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
@@ -17925,7 +17793,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17952,22 +17820,22 @@
       </c>
       <c r="D118" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5584363636363636</v>
+        <v>0.4507</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-126</v>
+        <v>122</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-120</v>
+        <v>126</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17991,7 +17859,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -18000,9 +17868,141 @@
         <v/>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers -1.5</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="I119" s="13">
+        <f>IF($H$119="","",IF($H$119&lt;0,-$H$119/(-$H$119+100),100/($H$119+100)))</f>
+        <v/>
+      </c>
+      <c r="J119" s="16">
+        <f>IF($H$119="","",$F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))</f>
+        <v/>
+      </c>
+      <c r="K119" s="17">
+        <f>IF($H$119="","",MAX(0,($F$119*IF($H$119&lt;0,-100/$H$119,$H$119/100)-(1-$F$119))/IF($H$119&lt;0,-100/$H$119,$H$119/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L119" s="18">
+        <f>IF($H$119="","",ROUND(MIN($K$119,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M119" s="12">
+        <f>IF($J$119="","",IF($J$119&lt;0,"Pass",IF($J$119&lt;'Settings'!$B$4,"Thin",IF($J$119&lt;0.06,"✅ Sharp band",IF($J$119&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N119" s="19" t="inlineStr">
+        <is>
+          <t>Model 39.6% (fair +152). Your call.</t>
+        </is>
+      </c>
+      <c r="O119" s="15" t="n"/>
+      <c r="P119" s="16">
+        <f>IF(OR($H$119="",$O$119=""),"",(1+IF($H$119&lt;0,-100/$H$119,$H$119/100))/(1+IF($O$119&lt;0,-100/$O$119,$O$119/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B120" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C120" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D120" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres +1.5</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>0.6036</v>
+      </c>
+      <c r="G120" s="14" t="n">
+        <v>-152</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="I120" s="13">
+        <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
+        <v/>
+      </c>
+      <c r="J120" s="16">
+        <f>IF($H$120="","",$F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))</f>
+        <v/>
+      </c>
+      <c r="K120" s="17">
+        <f>IF($H$120="","",MAX(0,($F$120*IF($H$120&lt;0,-100/$H$120,$H$120/100)-(1-$F$120))/IF($H$120&lt;0,-100/$H$120,$H$120/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L120" s="18">
+        <f>IF($H$120="","",ROUND(MIN($K$120,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M120" s="12">
+        <f>IF($J$120="","",IF($J$120&lt;0,"Pass",IF($J$120&lt;'Settings'!$B$4,"Thin",IF($J$120&lt;0.06,"✅ Sharp band",IF($J$120&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N120" s="19" t="inlineStr">
+        <is>
+          <t>Model 60.4% (fair -152). Your call.</t>
+        </is>
+      </c>
+      <c r="O120" s="15" t="n"/>
+      <c r="P120" s="16">
+        <f>IF(OR($H$120="",$O$120=""),"",(1+IF($H$120&lt;0,-100/$H$120,$H$120/100))/(1+IF($O$120&lt;0,-100/$O$120,$O$120/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J118">
+  <conditionalFormatting sqref="J5:J120">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -18168,13 +18168,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6545941176470589</v>
+        <v>0.653191304347826</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-190</v>
+        <v>-188</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-257</v>
+        <v>-245</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -18198,7 +18198,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -18234,10 +18234,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3453913043478261</v>
+        <v>0.3467826086956521</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>245</v>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -18432,10 +18432,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5478846153846153</v>
+        <v>0.6055</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-121</v>
+        <v>-153</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>108</v>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 60.6% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -18498,13 +18498,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.45215</v>
+        <v>0.3945</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 39.4% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -18564,13 +18564,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7068</v>
+        <v>0.711615587529976</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-241</v>
+        <v>-247</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-285</v>
+        <v>-317</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -18594,7 +18594,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -241). Your call.</t>
+          <t>Model 71.2% (fair -247). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -18630,13 +18630,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.293175</v>
+        <v>0.2884146341463415</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -18660,7 +18660,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +241). Your call.</t>
+          <t>Model 28.8% (fair +247). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -18696,13 +18696,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4191079812206573</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>139</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -18768,7 +18768,7 @@
         <v>-139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -18824,17 +18824,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Connecticut Sun +6.5</t>
+          <t>Connecticut Sun +7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5329</v>
+        <v>0.5641</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-114</v>
+        <v>-129</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -18890,17 +18890,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Dallas Wings -6.5</t>
+          <t>Dallas Wings -7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4671</v>
+        <v>0.4359</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -18960,13 +18960,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3692</v>
+        <v>0.3890573770491804</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -18990,7 +18990,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -19026,13 +19026,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.6308259259259259</v>
+        <v>0.61092</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-171</v>
+        <v>-157</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-170</v>
+        <v>-150</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -19088,17 +19088,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 170.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5</v>
+        <v>0.5234615384615384</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>100</v>
+        <v>-110</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -19122,7 +19122,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -19154,17 +19154,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 170.5</t>
+          <t>Under 169.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4765</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -19220,17 +19220,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Phoenix Mercury -5.5</t>
+          <t>Phoenix Mercury -4.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4574</v>
+        <v>0.4887</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -19254,7 +19254,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -19286,17 +19286,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Storm +5.5</t>
+          <t>Seattle Storm +4.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5426</v>
+        <v>0.5113</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-119</v>
+        <v>-105</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -19320,7 +19320,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -19435,28 +19435,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2496</v>
+        <v>0.2495</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4581</v>
+        <v>0.4515</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-1.73</v>
+        <v>-4.73</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-0.85</v>
+        <v>-2.3</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5028</v>
+        <v>0.5054</v>
       </c>
     </row>
     <row r="6">
@@ -19466,28 +19466,28 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>0.2511</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.4756</v>
+        <v>0.4671</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>0.92</v>
+        <v>-2.08</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.25</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>3.38</v>
+        <v>3.43</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="7">
@@ -19570,7 +19570,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=255, ECE 0.052 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=258, ECE 0.050 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -19665,16 +19665,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4575</v>
+        <v>0.4582</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4615</v>
+        <v>0.4625</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.004</v>
+        <v>0.0043</v>
       </c>
     </row>
     <row r="21">
@@ -19684,16 +19684,16 @@
         </is>
       </c>
       <c r="B21" s="21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>0.5429</v>
+        <v>0.5425</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>0.5204</v>
+        <v>0.5253</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>-0.0225</v>
+        <v>-0.0173</v>
       </c>
     </row>
     <row r="22">
